--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>127128041</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>127126721</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127127634</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>127126872</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>127126633</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127128041</v>
+        <v>127126721</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654928</v>
+        <v>654819</v>
       </c>
       <c r="R10" t="n">
-        <v>6648531</v>
+        <v>6648558</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1773,10 +1773,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127126721</v>
+        <v>127128041</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654819</v>
+        <v>654928</v>
       </c>
       <c r="R11" t="n">
-        <v>6648558</v>
+        <v>6648531</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1892,7 +1892,7 @@
         <v>127127634</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>127126872</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>127126633</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127126721</v>
+        <v>127128041</v>
       </c>
       <c r="B10" t="n">
         <v>98442</v>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654819</v>
+        <v>654928</v>
       </c>
       <c r="R10" t="n">
-        <v>6648558</v>
+        <v>6648531</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127128041</v>
+        <v>127126721</v>
       </c>
       <c r="B11" t="n">
         <v>98442</v>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654928</v>
+        <v>654819</v>
       </c>
       <c r="R11" t="n">
-        <v>6648531</v>
+        <v>6648558</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127128041</v>
+        <v>127126721</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654928</v>
+        <v>654819</v>
       </c>
       <c r="R10" t="n">
-        <v>6648531</v>
+        <v>6648558</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1773,10 +1773,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127126721</v>
+        <v>127128041</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654819</v>
+        <v>654928</v>
       </c>
       <c r="R11" t="n">
-        <v>6648558</v>
+        <v>6648531</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1892,7 +1892,7 @@
         <v>127127634</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>127126872</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>127126633</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127126721</v>
+        <v>127128041</v>
       </c>
       <c r="B10" t="n">
         <v>98443</v>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654819</v>
+        <v>654928</v>
       </c>
       <c r="R10" t="n">
-        <v>6648558</v>
+        <v>6648531</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127128041</v>
+        <v>127126721</v>
       </c>
       <c r="B11" t="n">
         <v>98443</v>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654928</v>
+        <v>654819</v>
       </c>
       <c r="R11" t="n">
-        <v>6648531</v>
+        <v>6648558</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127126872</v>
+        <v>127126633</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654832</v>
+        <v>654796</v>
       </c>
       <c r="R13" t="n">
-        <v>6648553</v>
+        <v>6648534</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127126633</v>
+        <v>127126872</v>
       </c>
       <c r="B14" t="n">
         <v>98443</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654796</v>
+        <v>654832</v>
       </c>
       <c r="R14" t="n">
-        <v>6648534</v>
+        <v>6648553</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -1548,7 +1548,7 @@
         <v>127126899</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127128041</v>
+        <v>127126721</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654928</v>
+        <v>654819</v>
       </c>
       <c r="R10" t="n">
-        <v>6648531</v>
+        <v>6648558</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1773,10 +1773,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127126721</v>
+        <v>127128041</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654819</v>
+        <v>654928</v>
       </c>
       <c r="R11" t="n">
-        <v>6648558</v>
+        <v>6648531</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1892,7 +1892,7 @@
         <v>127127634</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127126633</v>
+        <v>127126872</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654796</v>
+        <v>654832</v>
       </c>
       <c r="R13" t="n">
-        <v>6648534</v>
+        <v>6648553</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127126872</v>
+        <v>127126633</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654832</v>
+        <v>654796</v>
       </c>
       <c r="R14" t="n">
-        <v>6648553</v>
+        <v>6648534</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>127127868</v>
       </c>
       <c r="B15" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>127126833</v>
       </c>
       <c r="B16" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>127126721</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>127128041</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127127634</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>127126872</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>127126633</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -1548,7 +1548,7 @@
         <v>127126899</v>
       </c>
       <c r="B9" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127126721</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>127128041</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127127634</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127126872</v>
+        <v>127126633</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654832</v>
+        <v>654796</v>
       </c>
       <c r="R13" t="n">
-        <v>6648553</v>
+        <v>6648534</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127126633</v>
+        <v>127126872</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654796</v>
+        <v>654832</v>
       </c>
       <c r="R14" t="n">
-        <v>6648534</v>
+        <v>6648553</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -2005,7 +2005,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127126633</v>
+        <v>127126872</v>
       </c>
       <c r="B13" t="n">
         <v>98450</v>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654796</v>
+        <v>654832</v>
       </c>
       <c r="R13" t="n">
-        <v>6648534</v>
+        <v>6648553</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127126872</v>
+        <v>127126633</v>
       </c>
       <c r="B14" t="n">
         <v>98450</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654832</v>
+        <v>654796</v>
       </c>
       <c r="R14" t="n">
-        <v>6648553</v>
+        <v>6648534</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2459,6 +2459,4812 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127784378</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>654950</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6648519</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127781552</v>
+      </c>
+      <c r="B18" t="n">
+        <v>105488</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>654841</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6648625</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127781998</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>654769</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6648529</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127782688</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>654896</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6648627</v>
+      </c>
+      <c r="S20" t="n">
+        <v>9</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tiotalet bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127781937</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>654795</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6648542</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127782608</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>654882</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6648586</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127782340</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>654840</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6648541</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>5 fröst.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127781639</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>654834</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6648587</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127783233</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>654939</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6648547</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I asp. Även bohål st hack.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127783934</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>654911</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6648510</v>
+      </c>
+      <c r="S26" t="n">
+        <v>7</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127781082</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>654826</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6648657</v>
+      </c>
+      <c r="S27" t="n">
+        <v>7</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127784226</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>654947</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6648499</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127781864</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>654817</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6648561</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fyra fröställn.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127782599</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>654852</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6648592</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127781251</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>654836</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6648615</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Sex fröståndare inom 4 m radie. Minst 30 bladrosetter. Ca 20 m syd om hänsynssnitslad yta (fuktstråk m socklar).</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127780852</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>654829</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6648641</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>En fröställning. Utanför, syd om hänsynsyta som snitslat ett fuktstråk med glasbjörk och klibbal på socklar.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127785581</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>654763</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6648504</v>
+      </c>
+      <c r="S33" t="n">
+        <v>9</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127784246</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>654977</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6648526</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127784696</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>654903</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6648470</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127782582</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>654831</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6648582</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127783185</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>654900</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6648568</v>
+      </c>
+      <c r="S37" t="n">
+        <v>6</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127782751</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>654873</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6648648</v>
+      </c>
+      <c r="S38" t="n">
+        <v>12</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 25 bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127784050</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>654933</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6648492</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127782237</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>654811</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6648510</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>3 st</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127782716</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>654873</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6648615</v>
+      </c>
+      <c r="S41" t="n">
+        <v>8</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Tiotalet bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127783424</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>654926</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6648527</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127781723</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>654831</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6648568</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127781898</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>654812</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6648545</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>7 fröställn inom 3 m radie.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127781429</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>654841</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6648625</v>
+      </c>
+      <c r="S45" t="n">
+        <v>6</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127781122</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>654819</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6648643</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Bladrosett på norra snitslingsavgränsningen hänsynsyta.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127782650</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>654890</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6648616</v>
+      </c>
+      <c r="S47" t="n">
+        <v>9</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127784001</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>654913</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6648493</v>
+      </c>
+      <c r="S48" t="n">
+        <v>9</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127784278</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>654961</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6648515</v>
+      </c>
+      <c r="S49" t="n">
+        <v>7</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127782845</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>654847</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6648610</v>
+      </c>
+      <c r="S50" t="n">
+        <v>6</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127780501</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>654892</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6648647</v>
+      </c>
+      <c r="S51" t="n">
+        <v>12</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127782527</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>654840</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6648555</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127781961</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>654782</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6648543</v>
+      </c>
+      <c r="S53" t="n">
+        <v>7</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127785899</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>654819</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6648643</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127782275</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>654824</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6648522</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127783912</v>
+      </c>
+      <c r="B56" t="n">
+        <v>105488</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>654926</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6648527</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127782436</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>654829</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6648541</v>
+      </c>
+      <c r="S57" t="n">
+        <v>6</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127782081</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>654807</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6648524</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>6 fröställn</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -2461,32 +2461,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127784378</v>
+        <v>127781552</v>
       </c>
       <c r="B17" t="n">
-        <v>98450</v>
+        <v>105488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654950</v>
+        <v>654841</v>
       </c>
       <c r="R17" t="n">
-        <v>6648519</v>
+        <v>6648625</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,32 +2573,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127781552</v>
+        <v>127784378</v>
       </c>
       <c r="B18" t="n">
-        <v>105488</v>
+        <v>98450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654841</v>
+        <v>654950</v>
       </c>
       <c r="R18" t="n">
-        <v>6648625</v>
+        <v>6648519</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2802,7 +2802,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127782688</v>
+        <v>127781937</v>
       </c>
       <c r="B20" t="n">
         <v>98450</v>
@@ -2833,7 +2833,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654896</v>
+        <v>654795</v>
       </c>
       <c r="R20" t="n">
-        <v>6648627</v>
+        <v>6648542</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2887,12 +2887,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tiotalet bladrosetter.</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2919,7 +2914,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127781937</v>
+        <v>127782688</v>
       </c>
       <c r="B21" t="n">
         <v>98450</v>
@@ -2950,7 +2945,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2959,13 +2954,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654795</v>
+        <v>654896</v>
       </c>
       <c r="R21" t="n">
-        <v>6648542</v>
+        <v>6648627</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2994,7 +2989,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,7 +2999,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tiotalet bladrosetter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3031,7 +3031,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127782608</v>
+        <v>127781639</v>
       </c>
       <c r="B22" t="n">
         <v>98450</v>
@@ -3071,13 +3071,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654882</v>
+        <v>654834</v>
       </c>
       <c r="R22" t="n">
-        <v>6648586</v>
+        <v>6648587</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3143,7 +3143,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782340</v>
+        <v>127782608</v>
       </c>
       <c r="B23" t="n">
         <v>98450</v>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654840</v>
+        <v>654882</v>
       </c>
       <c r="R23" t="n">
-        <v>6648541</v>
+        <v>6648586</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3228,12 +3228,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>5 fröst.</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3260,7 +3255,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127781639</v>
+        <v>127782340</v>
       </c>
       <c r="B24" t="n">
         <v>98450</v>
@@ -3300,13 +3295,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654834</v>
+        <v>654840</v>
       </c>
       <c r="R24" t="n">
-        <v>6648587</v>
+        <v>6648541</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3335,7 +3330,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3345,7 +3340,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>5 fröst.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3489,7 +3489,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127783934</v>
+        <v>127781082</v>
       </c>
       <c r="B26" t="n">
         <v>98450</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654911</v>
+        <v>654826</v>
       </c>
       <c r="R26" t="n">
-        <v>6648510</v>
+        <v>6648657</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3574,7 +3574,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3601,7 +3606,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127781082</v>
+        <v>127783934</v>
       </c>
       <c r="B27" t="n">
         <v>98450</v>
@@ -3641,10 +3646,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654826</v>
+        <v>654911</v>
       </c>
       <c r="R27" t="n">
-        <v>6648657</v>
+        <v>6648510</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
@@ -3676,7 +3681,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3686,12 +3691,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3947,7 +3947,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127782599</v>
+        <v>127780852</v>
       </c>
       <c r="B30" t="n">
         <v>98450</v>
@@ -3987,13 +3987,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654852</v>
+        <v>654829</v>
       </c>
       <c r="R30" t="n">
-        <v>6648592</v>
+        <v>6648641</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4032,7 +4032,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>En fröställning. Utanför, syd om hänsynsyta som snitslat ett fuktstråk med glasbjörk och klibbal på socklar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4059,7 +4064,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127781251</v>
+        <v>127782599</v>
       </c>
       <c r="B31" t="n">
         <v>98450</v>
@@ -4099,13 +4104,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654836</v>
+        <v>654852</v>
       </c>
       <c r="R31" t="n">
-        <v>6648615</v>
+        <v>6648592</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4134,7 +4139,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4144,12 +4149,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Sex fröståndare inom 4 m radie. Minst 30 bladrosetter. Ca 20 m syd om hänsynssnitslad yta (fuktstråk m socklar).</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4176,7 +4176,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127780852</v>
+        <v>127784696</v>
       </c>
       <c r="B32" t="n">
         <v>98450</v>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654829</v>
+        <v>654903</v>
       </c>
       <c r="R32" t="n">
-        <v>6648641</v>
+        <v>6648470</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4261,12 +4261,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>En fröställning. Utanför, syd om hänsynsyta som snitslat ett fuktstråk med glasbjörk och klibbal på socklar.</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4293,7 +4288,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127785581</v>
+        <v>127781251</v>
       </c>
       <c r="B33" t="n">
         <v>98450</v>
@@ -4333,13 +4328,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654763</v>
+        <v>654836</v>
       </c>
       <c r="R33" t="n">
-        <v>6648504</v>
+        <v>6648615</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4368,7 +4363,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4378,7 +4373,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Sex fröståndare inom 4 m radie. Minst 30 bladrosetter. Ca 20 m syd om hänsynssnitslad yta (fuktstråk m socklar).</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4517,7 +4517,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127784696</v>
+        <v>127785581</v>
       </c>
       <c r="B35" t="n">
         <v>98450</v>
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654903</v>
+        <v>654763</v>
       </c>
       <c r="R35" t="n">
-        <v>6648470</v>
+        <v>6648504</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4853,7 +4853,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127782751</v>
+        <v>127784050</v>
       </c>
       <c r="B38" t="n">
         <v>98450</v>
@@ -4893,13 +4893,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654873</v>
+        <v>654933</v>
       </c>
       <c r="R38" t="n">
-        <v>6648648</v>
+        <v>6648492</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4938,12 +4938,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 25 bladrosetter.</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4970,7 +4965,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127784050</v>
+        <v>127782751</v>
       </c>
       <c r="B39" t="n">
         <v>98450</v>
@@ -5010,13 +5005,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654933</v>
+        <v>654873</v>
       </c>
       <c r="R39" t="n">
-        <v>6648492</v>
+        <v>6648648</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5045,7 +5040,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5055,7 +5050,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 25 bladrosetter.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5082,7 +5082,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127782237</v>
+        <v>127781723</v>
       </c>
       <c r="B40" t="n">
         <v>98450</v>
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654811</v>
+        <v>654831</v>
       </c>
       <c r="R40" t="n">
-        <v>6648510</v>
+        <v>6648568</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,7 +5199,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127782716</v>
+        <v>127782237</v>
       </c>
       <c r="B41" t="n">
         <v>98450</v>
@@ -5230,7 +5230,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5239,13 +5239,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654873</v>
+        <v>654811</v>
       </c>
       <c r="R41" t="n">
-        <v>6648615</v>
+        <v>6648510</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Tiotalet bladrosetter</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5316,7 +5316,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127783424</v>
+        <v>127781429</v>
       </c>
       <c r="B42" t="n">
         <v>98450</v>
@@ -5347,7 +5347,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5356,13 +5356,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654926</v>
+        <v>654841</v>
       </c>
       <c r="R42" t="n">
-        <v>6648527</v>
+        <v>6648625</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
+          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5433,7 +5433,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127781723</v>
+        <v>127781898</v>
       </c>
       <c r="B43" t="n">
         <v>98450</v>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654831</v>
+        <v>654812</v>
       </c>
       <c r="R43" t="n">
-        <v>6648568</v>
+        <v>6648545</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
+          <t>7 fröställn inom 3 m radie.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5550,7 +5550,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127781898</v>
+        <v>127782716</v>
       </c>
       <c r="B44" t="n">
         <v>98450</v>
@@ -5581,7 +5581,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5590,13 +5590,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654812</v>
+        <v>654873</v>
       </c>
       <c r="R44" t="n">
-        <v>6648545</v>
+        <v>6648615</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5635,12 +5635,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>7 fröställn inom 3 m radie.</t>
+          <t>Tiotalet bladrosetter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5667,7 +5667,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127781429</v>
+        <v>127783424</v>
       </c>
       <c r="B45" t="n">
         <v>98450</v>
@@ -5698,7 +5698,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654841</v>
+        <v>654926</v>
       </c>
       <c r="R45" t="n">
-        <v>6648625</v>
+        <v>6648527</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
+          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5901,7 +5901,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127782650</v>
+        <v>127784278</v>
       </c>
       <c r="B47" t="n">
         <v>98450</v>
@@ -5932,7 +5932,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654890</v>
+        <v>654961</v>
       </c>
       <c r="R47" t="n">
-        <v>6648616</v>
+        <v>6648515</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6125,7 +6125,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127784278</v>
+        <v>127782650</v>
       </c>
       <c r="B49" t="n">
         <v>98450</v>
@@ -6156,7 +6156,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6165,13 +6165,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654961</v>
+        <v>654890</v>
       </c>
       <c r="R49" t="n">
-        <v>6648515</v>
+        <v>6648616</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6461,53 +6461,60 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127782527</v>
+        <v>127785899</v>
       </c>
       <c r="B52" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654840</v>
+        <v>654819</v>
       </c>
       <c r="R52" t="n">
-        <v>6648555</v>
+        <v>6648643</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6536,7 +6543,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6546,7 +6553,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6685,60 +6697,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127785899</v>
+        <v>127782527</v>
       </c>
       <c r="B54" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654819</v>
+        <v>654840</v>
       </c>
       <c r="R54" t="n">
-        <v>6648643</v>
+        <v>6648555</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6767,7 +6772,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6777,12 +6782,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>127126721</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>127128041</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127127634</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127126872</v>
+        <v>127126633</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654832</v>
+        <v>654796</v>
       </c>
       <c r="R13" t="n">
-        <v>6648553</v>
+        <v>6648534</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127126633</v>
+        <v>127126872</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654796</v>
+        <v>654832</v>
       </c>
       <c r="R14" t="n">
-        <v>6648534</v>
+        <v>6648553</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2461,38 +2461,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127781552</v>
+        <v>127781998</v>
       </c>
       <c r="B17" t="n">
-        <v>105488</v>
+        <v>98456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654841</v>
+        <v>654769</v>
       </c>
       <c r="R17" t="n">
-        <v>6648625</v>
+        <v>6648529</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,7 +2546,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,32 +2578,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127784378</v>
+        <v>127781552</v>
       </c>
       <c r="B18" t="n">
-        <v>98450</v>
+        <v>105494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2613,13 +2618,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654950</v>
+        <v>654841</v>
       </c>
       <c r="R18" t="n">
-        <v>6648519</v>
+        <v>6648625</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2648,7 +2653,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,7 +2663,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2685,10 +2690,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127781998</v>
+        <v>127784378</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2716,7 +2721,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2725,13 +2730,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654769</v>
+        <v>654950</v>
       </c>
       <c r="R19" t="n">
-        <v>6648529</v>
+        <v>6648519</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2760,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2770,12 +2775,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2802,10 +2802,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127781937</v>
+        <v>127782688</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654795</v>
+        <v>654896</v>
       </c>
       <c r="R20" t="n">
-        <v>6648542</v>
+        <v>6648627</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2887,7 +2887,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tiotalet bladrosetter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2914,10 +2919,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127782688</v>
+        <v>127781937</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2950,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2954,13 +2959,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654896</v>
+        <v>654795</v>
       </c>
       <c r="R21" t="n">
-        <v>6648627</v>
+        <v>6648542</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2989,7 +2994,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2999,12 +3004,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tiotalet bladrosetter.</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3034,7 +3034,7 @@
         <v>127781639</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782608</v>
+        <v>127782340</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654882</v>
+        <v>654840</v>
       </c>
       <c r="R23" t="n">
-        <v>6648586</v>
+        <v>6648541</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3228,7 +3228,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>5 fröst.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3255,10 +3260,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127782340</v>
+        <v>127782608</v>
       </c>
       <c r="B24" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3295,10 +3300,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654840</v>
+        <v>654882</v>
       </c>
       <c r="R24" t="n">
-        <v>6648541</v>
+        <v>6648586</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3330,7 +3335,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3340,12 +3345,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>5 fröst.</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3372,38 +3372,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127783233</v>
+        <v>127783934</v>
       </c>
       <c r="B25" t="n">
-        <v>57660</v>
+        <v>98456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654939</v>
+        <v>654911</v>
       </c>
       <c r="R25" t="n">
-        <v>6648547</v>
+        <v>6648510</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,12 +3457,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:52</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>I asp. Även bohål st hack.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3492,7 +3487,7 @@
         <v>127781082</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3606,38 +3601,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127783934</v>
+        <v>127783233</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3646,13 +3641,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654911</v>
+        <v>654939</v>
       </c>
       <c r="R27" t="n">
-        <v>6648510</v>
+        <v>6648547</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3681,7 +3676,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3691,7 +3686,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>I asp. Även bohål st hack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3721,7 +3721,7 @@
         <v>127784226</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>127781864</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>127780852</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127782599</v>
+        <v>127785581</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654852</v>
+        <v>654763</v>
       </c>
       <c r="R31" t="n">
-        <v>6648592</v>
+        <v>6648504</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4176,10 +4176,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127784696</v>
+        <v>127782599</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4216,13 +4216,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654903</v>
+        <v>654852</v>
       </c>
       <c r="R32" t="n">
-        <v>6648470</v>
+        <v>6648592</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4291,7 +4291,7 @@
         <v>127781251</v>
       </c>
       <c r="B33" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>127784246</v>
       </c>
       <c r="B34" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127785581</v>
+        <v>127784696</v>
       </c>
       <c r="B35" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654763</v>
+        <v>654903</v>
       </c>
       <c r="R35" t="n">
-        <v>6648504</v>
+        <v>6648470</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4629,10 +4629,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127782582</v>
+        <v>127783185</v>
       </c>
       <c r="B36" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,24 +4658,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654831</v>
+        <v>654900</v>
       </c>
       <c r="R36" t="n">
-        <v>6648582</v>
+        <v>6648568</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4704,7 +4699,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4714,7 +4709,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127783185</v>
+        <v>127782582</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4770,19 +4770,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654900</v>
+        <v>654831</v>
       </c>
       <c r="R37" t="n">
-        <v>6648568</v>
+        <v>6648582</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4811,7 +4816,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4821,12 +4826,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4856,7 +4856,7 @@
         <v>127784050</v>
       </c>
       <c r="B38" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>127782751</v>
       </c>
       <c r="B39" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127781723</v>
+        <v>127783424</v>
       </c>
       <c r="B40" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654831</v>
+        <v>654926</v>
       </c>
       <c r="R40" t="n">
-        <v>6648568</v>
+        <v>6648527</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
+          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,10 +5199,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127782237</v>
+        <v>127781429</v>
       </c>
       <c r="B41" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5239,13 +5239,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654811</v>
+        <v>654841</v>
       </c>
       <c r="R41" t="n">
-        <v>6648510</v>
+        <v>6648625</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5316,10 +5316,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127781429</v>
+        <v>127781898</v>
       </c>
       <c r="B42" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5356,13 +5356,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654841</v>
+        <v>654812</v>
       </c>
       <c r="R42" t="n">
-        <v>6648625</v>
+        <v>6648545</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
+          <t>7 fröställn inom 3 m radie.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127781898</v>
+        <v>127781723</v>
       </c>
       <c r="B43" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654812</v>
+        <v>654831</v>
       </c>
       <c r="R43" t="n">
-        <v>6648545</v>
+        <v>6648568</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>7 fröställn inom 3 m radie.</t>
+          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5553,7 +5553,7 @@
         <v>127782716</v>
       </c>
       <c r="B44" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5667,10 +5667,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127783424</v>
+        <v>127782237</v>
       </c>
       <c r="B45" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654926</v>
+        <v>654811</v>
       </c>
       <c r="R45" t="n">
-        <v>6648527</v>
+        <v>6648510</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5787,7 +5787,7 @@
         <v>127781122</v>
       </c>
       <c r="B46" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>127784278</v>
       </c>
       <c r="B47" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>127784001</v>
       </c>
       <c r="B48" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>127782650</v>
       </c>
       <c r="B49" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>127782845</v>
       </c>
       <c r="B50" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>127780501</v>
       </c>
       <c r="B51" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>127781961</v>
       </c>
       <c r="B53" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>127782527</v>
       </c>
       <c r="B54" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>127782275</v>
       </c>
       <c r="B55" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6921,38 +6921,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127783912</v>
+        <v>127782081</v>
       </c>
       <c r="B56" t="n">
-        <v>105488</v>
+        <v>98456</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654926</v>
+        <v>654807</v>
       </c>
       <c r="R56" t="n">
-        <v>6648527</v>
+        <v>6648524</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7006,7 +7006,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>6 fröställn</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7036,7 +7041,7 @@
         <v>127782436</v>
       </c>
       <c r="B57" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7150,38 +7155,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127782081</v>
+        <v>127783912</v>
       </c>
       <c r="B58" t="n">
-        <v>98450</v>
+        <v>105494</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7190,10 +7195,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654807</v>
+        <v>654926</v>
       </c>
       <c r="R58" t="n">
-        <v>6648524</v>
+        <v>6648527</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7225,7 +7230,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7235,12 +7240,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>6 fröställn</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -1548,7 +1548,7 @@
         <v>127126899</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127126721</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>127128041</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127127634</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127126633</v>
+        <v>127126872</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654796</v>
+        <v>654832</v>
       </c>
       <c r="R13" t="n">
-        <v>6648534</v>
+        <v>6648553</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127126872</v>
+        <v>127126633</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654832</v>
+        <v>654796</v>
       </c>
       <c r="R14" t="n">
-        <v>6648553</v>
+        <v>6648534</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2461,38 +2461,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127781998</v>
+        <v>127781552</v>
       </c>
       <c r="B17" t="n">
-        <v>98456</v>
+        <v>105497</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654769</v>
+        <v>654841</v>
       </c>
       <c r="R17" t="n">
-        <v>6648529</v>
+        <v>6648625</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,12 +2546,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2578,32 +2573,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127781552</v>
+        <v>127784378</v>
       </c>
       <c r="B18" t="n">
-        <v>105494</v>
+        <v>98459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2618,13 +2613,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654841</v>
+        <v>654950</v>
       </c>
       <c r="R18" t="n">
-        <v>6648625</v>
+        <v>6648519</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2653,7 +2648,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2663,7 +2658,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2690,10 +2685,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127784378</v>
+        <v>127781998</v>
       </c>
       <c r="B19" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2716,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2730,13 +2725,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654950</v>
+        <v>654769</v>
       </c>
       <c r="R19" t="n">
-        <v>6648519</v>
+        <v>6648529</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2765,7 +2760,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,7 +2770,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2802,10 +2802,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127782688</v>
+        <v>127781937</v>
       </c>
       <c r="B20" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654896</v>
+        <v>654795</v>
       </c>
       <c r="R20" t="n">
-        <v>6648627</v>
+        <v>6648542</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2887,12 +2887,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tiotalet bladrosetter.</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2919,10 +2914,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127781937</v>
+        <v>127782688</v>
       </c>
       <c r="B21" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2950,7 +2945,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2959,13 +2954,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654795</v>
+        <v>654896</v>
       </c>
       <c r="R21" t="n">
-        <v>6648542</v>
+        <v>6648627</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2994,7 +2989,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,7 +2999,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tiotalet bladrosetter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3034,7 +3034,7 @@
         <v>127781639</v>
       </c>
       <c r="B22" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782340</v>
+        <v>127782608</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654840</v>
+        <v>654882</v>
       </c>
       <c r="R23" t="n">
-        <v>6648541</v>
+        <v>6648586</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3228,12 +3228,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>5 fröst.</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3260,10 +3255,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127782608</v>
+        <v>127782340</v>
       </c>
       <c r="B24" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3300,10 +3295,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654882</v>
+        <v>654840</v>
       </c>
       <c r="R24" t="n">
-        <v>6648586</v>
+        <v>6648541</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3335,7 +3330,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3345,7 +3340,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>5 fröst.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3372,38 +3372,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127783934</v>
+        <v>127783233</v>
       </c>
       <c r="B25" t="n">
-        <v>98456</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654911</v>
+        <v>654939</v>
       </c>
       <c r="R25" t="n">
-        <v>6648510</v>
+        <v>6648547</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,7 +3457,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I asp. Även bohål st hack.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3487,7 +3492,7 @@
         <v>127781082</v>
       </c>
       <c r="B26" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,38 +3606,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127783233</v>
+        <v>127783934</v>
       </c>
       <c r="B27" t="n">
-        <v>57660</v>
+        <v>98459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3641,13 +3646,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654939</v>
+        <v>654911</v>
       </c>
       <c r="R27" t="n">
-        <v>6648547</v>
+        <v>6648510</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3676,7 +3681,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3686,12 +3691,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:52</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>I asp. Även bohål st hack.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3721,7 +3721,7 @@
         <v>127784226</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>127781864</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>127780852</v>
       </c>
       <c r="B30" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127785581</v>
+        <v>127782599</v>
       </c>
       <c r="B31" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654763</v>
+        <v>654852</v>
       </c>
       <c r="R31" t="n">
-        <v>6648504</v>
+        <v>6648592</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4176,10 +4176,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127782599</v>
+        <v>127784696</v>
       </c>
       <c r="B32" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4216,13 +4216,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654852</v>
+        <v>654903</v>
       </c>
       <c r="R32" t="n">
-        <v>6648592</v>
+        <v>6648470</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4291,7 +4291,7 @@
         <v>127781251</v>
       </c>
       <c r="B33" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>127784246</v>
       </c>
       <c r="B34" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127784696</v>
+        <v>127785581</v>
       </c>
       <c r="B35" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654903</v>
+        <v>654763</v>
       </c>
       <c r="R35" t="n">
-        <v>6648470</v>
+        <v>6648504</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4629,10 +4629,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127783185</v>
+        <v>127782582</v>
       </c>
       <c r="B36" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,19 +4658,24 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654900</v>
+        <v>654831</v>
       </c>
       <c r="R36" t="n">
-        <v>6648568</v>
+        <v>6648582</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4699,7 +4704,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4709,12 +4714,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127782582</v>
+        <v>127783185</v>
       </c>
       <c r="B37" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4770,24 +4770,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654831</v>
+        <v>654900</v>
       </c>
       <c r="R37" t="n">
-        <v>6648582</v>
+        <v>6648568</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4816,7 +4811,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4826,7 +4821,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4856,7 +4856,7 @@
         <v>127784050</v>
       </c>
       <c r="B38" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>127782751</v>
       </c>
       <c r="B39" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127783424</v>
+        <v>127781723</v>
       </c>
       <c r="B40" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654926</v>
+        <v>654831</v>
       </c>
       <c r="R40" t="n">
-        <v>6648527</v>
+        <v>6648568</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
+          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,10 +5199,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127781429</v>
+        <v>127782237</v>
       </c>
       <c r="B41" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5239,13 +5239,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654841</v>
+        <v>654811</v>
       </c>
       <c r="R41" t="n">
-        <v>6648625</v>
+        <v>6648510</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5316,10 +5316,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127781898</v>
+        <v>127781429</v>
       </c>
       <c r="B42" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5356,13 +5356,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654812</v>
+        <v>654841</v>
       </c>
       <c r="R42" t="n">
-        <v>6648545</v>
+        <v>6648625</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>7 fröställn inom 3 m radie.</t>
+          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127781723</v>
+        <v>127781898</v>
       </c>
       <c r="B43" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654831</v>
+        <v>654812</v>
       </c>
       <c r="R43" t="n">
-        <v>6648568</v>
+        <v>6648545</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
+          <t>7 fröställn inom 3 m radie.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5553,7 +5553,7 @@
         <v>127782716</v>
       </c>
       <c r="B44" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5667,10 +5667,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127782237</v>
+        <v>127783424</v>
       </c>
       <c r="B45" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654811</v>
+        <v>654926</v>
       </c>
       <c r="R45" t="n">
-        <v>6648510</v>
+        <v>6648527</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5787,7 +5787,7 @@
         <v>127781122</v>
       </c>
       <c r="B46" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127784278</v>
+        <v>127782650</v>
       </c>
       <c r="B47" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654961</v>
+        <v>654890</v>
       </c>
       <c r="R47" t="n">
-        <v>6648515</v>
+        <v>6648616</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6013,10 +6013,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127784001</v>
+        <v>127784278</v>
       </c>
       <c r="B48" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6053,13 +6053,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654913</v>
+        <v>654961</v>
       </c>
       <c r="R48" t="n">
-        <v>6648493</v>
+        <v>6648515</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6125,10 +6125,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127782650</v>
+        <v>127784001</v>
       </c>
       <c r="B49" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6165,10 +6165,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654890</v>
+        <v>654913</v>
       </c>
       <c r="R49" t="n">
-        <v>6648616</v>
+        <v>6648493</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6240,7 +6240,7 @@
         <v>127782845</v>
       </c>
       <c r="B50" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>127780501</v>
       </c>
       <c r="B51" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6461,60 +6461,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127785899</v>
+        <v>127781961</v>
       </c>
       <c r="B52" t="n">
-        <v>57823</v>
+        <v>98459</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654819</v>
+        <v>654782</v>
       </c>
       <c r="R52" t="n">
-        <v>6648643</v>
+        <v>6648543</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6543,7 +6536,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6553,12 +6546,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6585,10 +6573,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127781961</v>
+        <v>127782527</v>
       </c>
       <c r="B53" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6625,13 +6613,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654782</v>
+        <v>654840</v>
       </c>
       <c r="R53" t="n">
-        <v>6648543</v>
+        <v>6648555</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6660,7 +6648,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6670,7 +6658,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6697,53 +6685,60 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127782527</v>
+        <v>127785899</v>
       </c>
       <c r="B54" t="n">
-        <v>98456</v>
+        <v>57826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654840</v>
+        <v>654819</v>
       </c>
       <c r="R54" t="n">
-        <v>6648555</v>
+        <v>6648643</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6772,7 +6767,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6782,7 +6777,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6812,7 +6812,7 @@
         <v>127782275</v>
       </c>
       <c r="B55" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6921,38 +6921,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127782081</v>
+        <v>127783912</v>
       </c>
       <c r="B56" t="n">
-        <v>98456</v>
+        <v>105497</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654807</v>
+        <v>654926</v>
       </c>
       <c r="R56" t="n">
-        <v>6648524</v>
+        <v>6648527</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7006,12 +7006,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>6 fröställn</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7041,7 +7036,7 @@
         <v>127782436</v>
       </c>
       <c r="B57" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7155,38 +7150,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127783912</v>
+        <v>127782081</v>
       </c>
       <c r="B58" t="n">
-        <v>105494</v>
+        <v>98459</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7195,10 +7190,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654926</v>
+        <v>654807</v>
       </c>
       <c r="R58" t="n">
-        <v>6648527</v>
+        <v>6648524</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7230,7 +7225,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7240,7 +7235,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>6 fröställn</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -1548,7 +1548,7 @@
         <v>127126899</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127126721</v>
+        <v>127128041</v>
       </c>
       <c r="B10" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654819</v>
+        <v>654928</v>
       </c>
       <c r="R10" t="n">
-        <v>6648558</v>
+        <v>6648531</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1773,10 +1773,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127128041</v>
+        <v>127126721</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654928</v>
+        <v>654819</v>
       </c>
       <c r="R11" t="n">
-        <v>6648531</v>
+        <v>6648558</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1892,7 +1892,7 @@
         <v>127127634</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127126872</v>
+        <v>127126633</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654832</v>
+        <v>654796</v>
       </c>
       <c r="R13" t="n">
-        <v>6648553</v>
+        <v>6648534</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127126633</v>
+        <v>127126872</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654796</v>
+        <v>654832</v>
       </c>
       <c r="R14" t="n">
-        <v>6648534</v>
+        <v>6648553</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2461,32 +2461,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127781552</v>
+        <v>127784378</v>
       </c>
       <c r="B17" t="n">
-        <v>105497</v>
+        <v>98467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654841</v>
+        <v>654950</v>
       </c>
       <c r="R17" t="n">
-        <v>6648625</v>
+        <v>6648519</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,10 +2573,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127784378</v>
+        <v>127781998</v>
       </c>
       <c r="B18" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654950</v>
+        <v>654769</v>
       </c>
       <c r="R18" t="n">
-        <v>6648519</v>
+        <v>6648529</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,7 +2658,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2685,38 +2690,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127781998</v>
+        <v>127781552</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>105505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2725,13 +2730,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654769</v>
+        <v>654841</v>
       </c>
       <c r="R19" t="n">
-        <v>6648529</v>
+        <v>6648625</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2760,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2770,12 +2775,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2802,10 +2802,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127781937</v>
+        <v>127782688</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654795</v>
+        <v>654896</v>
       </c>
       <c r="R20" t="n">
-        <v>6648542</v>
+        <v>6648627</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2887,7 +2887,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tiotalet bladrosetter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2914,10 +2919,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127782688</v>
+        <v>127781937</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2950,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2954,13 +2959,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654896</v>
+        <v>654795</v>
       </c>
       <c r="R21" t="n">
-        <v>6648627</v>
+        <v>6648542</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2989,7 +2994,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2999,12 +3004,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tiotalet bladrosetter.</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3034,7 +3034,7 @@
         <v>127781639</v>
       </c>
       <c r="B22" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>127782608</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>127782340</v>
       </c>
       <c r="B24" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,38 +3372,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127783233</v>
+        <v>127783934</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>98467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654939</v>
+        <v>654911</v>
       </c>
       <c r="R25" t="n">
-        <v>6648547</v>
+        <v>6648510</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,12 +3457,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:52</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>I asp. Även bohål st hack.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3489,38 +3484,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127781082</v>
+        <v>127783233</v>
       </c>
       <c r="B26" t="n">
-        <v>98459</v>
+        <v>57669</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3529,13 +3524,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654826</v>
+        <v>654939</v>
       </c>
       <c r="R26" t="n">
-        <v>6648657</v>
+        <v>6648547</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3564,7 +3559,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3574,12 +3569,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
+          <t>I asp. Även bohål st hack.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3606,10 +3601,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127783934</v>
+        <v>127781082</v>
       </c>
       <c r="B27" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3646,10 +3641,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654911</v>
+        <v>654826</v>
       </c>
       <c r="R27" t="n">
-        <v>6648510</v>
+        <v>6648657</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
@@ -3681,7 +3676,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3691,7 +3686,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3721,7 +3721,7 @@
         <v>127784226</v>
       </c>
       <c r="B28" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>127781864</v>
       </c>
       <c r="B29" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127780852</v>
+        <v>127782599</v>
       </c>
       <c r="B30" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3987,13 +3987,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654829</v>
+        <v>654852</v>
       </c>
       <c r="R30" t="n">
-        <v>6648641</v>
+        <v>6648592</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4032,12 +4032,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>En fröställning. Utanför, syd om hänsynsyta som snitslat ett fuktstråk med glasbjörk och klibbal på socklar.</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4064,10 +4059,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127782599</v>
+        <v>127780852</v>
       </c>
       <c r="B31" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4104,13 +4099,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654852</v>
+        <v>654829</v>
       </c>
       <c r="R31" t="n">
-        <v>6648592</v>
+        <v>6648641</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4139,7 +4134,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4149,7 +4144,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>En fröställning. Utanför, syd om hänsynsyta som snitslat ett fuktstråk med glasbjörk och klibbal på socklar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4176,10 +4176,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127784696</v>
+        <v>127785581</v>
       </c>
       <c r="B32" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4216,13 +4216,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654903</v>
+        <v>654763</v>
       </c>
       <c r="R32" t="n">
-        <v>6648470</v>
+        <v>6648504</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4291,7 +4291,7 @@
         <v>127781251</v>
       </c>
       <c r="B33" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>127784246</v>
       </c>
       <c r="B34" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127785581</v>
+        <v>127784696</v>
       </c>
       <c r="B35" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654763</v>
+        <v>654903</v>
       </c>
       <c r="R35" t="n">
-        <v>6648504</v>
+        <v>6648470</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4629,10 +4629,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127782582</v>
+        <v>127783185</v>
       </c>
       <c r="B36" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,24 +4658,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654831</v>
+        <v>654900</v>
       </c>
       <c r="R36" t="n">
-        <v>6648582</v>
+        <v>6648568</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4704,7 +4699,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4714,7 +4709,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127783185</v>
+        <v>127782582</v>
       </c>
       <c r="B37" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4770,19 +4770,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654900</v>
+        <v>654831</v>
       </c>
       <c r="R37" t="n">
-        <v>6648568</v>
+        <v>6648582</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4811,7 +4816,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4821,12 +4826,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4856,7 +4856,7 @@
         <v>127784050</v>
       </c>
       <c r="B38" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>127782751</v>
       </c>
       <c r="B39" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127781723</v>
+        <v>127782237</v>
       </c>
       <c r="B40" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654831</v>
+        <v>654811</v>
       </c>
       <c r="R40" t="n">
-        <v>6648568</v>
+        <v>6648510</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,10 +5199,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127782237</v>
+        <v>127781898</v>
       </c>
       <c r="B41" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5239,13 +5239,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654811</v>
+        <v>654812</v>
       </c>
       <c r="R41" t="n">
-        <v>6648510</v>
+        <v>6648545</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>7 fröställn inom 3 m radie.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5319,7 +5319,7 @@
         <v>127781429</v>
       </c>
       <c r="B42" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127781898</v>
+        <v>127781723</v>
       </c>
       <c r="B43" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654812</v>
+        <v>654831</v>
       </c>
       <c r="R43" t="n">
-        <v>6648545</v>
+        <v>6648568</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>7 fröställn inom 3 m radie.</t>
+          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5553,7 +5553,7 @@
         <v>127782716</v>
       </c>
       <c r="B44" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>127783424</v>
       </c>
       <c r="B45" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>127781122</v>
       </c>
       <c r="B46" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>127782650</v>
       </c>
       <c r="B47" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>127784278</v>
       </c>
       <c r="B48" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>127784001</v>
       </c>
       <c r="B49" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6237,10 +6237,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127782845</v>
+        <v>127780501</v>
       </c>
       <c r="B50" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654847</v>
+        <v>654892</v>
       </c>
       <c r="R50" t="n">
-        <v>6648610</v>
+        <v>6648647</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6349,10 +6349,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127780501</v>
+        <v>127782845</v>
       </c>
       <c r="B51" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6389,13 +6389,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654892</v>
+        <v>654847</v>
       </c>
       <c r="R51" t="n">
-        <v>6648647</v>
+        <v>6648610</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6461,53 +6461,60 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127781961</v>
+        <v>127785899</v>
       </c>
       <c r="B52" t="n">
-        <v>98459</v>
+        <v>57832</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654782</v>
+        <v>654819</v>
       </c>
       <c r="R52" t="n">
-        <v>6648543</v>
+        <v>6648643</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6536,7 +6543,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6546,7 +6553,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6573,10 +6585,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127782527</v>
+        <v>127781961</v>
       </c>
       <c r="B53" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6613,13 +6625,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654840</v>
+        <v>654782</v>
       </c>
       <c r="R53" t="n">
-        <v>6648555</v>
+        <v>6648543</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6648,7 +6660,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6658,7 +6670,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6685,60 +6697,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127785899</v>
+        <v>127782527</v>
       </c>
       <c r="B54" t="n">
-        <v>57826</v>
+        <v>98467</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654819</v>
+        <v>654840</v>
       </c>
       <c r="R54" t="n">
-        <v>6648643</v>
+        <v>6648555</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6767,7 +6772,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6777,12 +6782,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6812,7 +6812,7 @@
         <v>127782275</v>
       </c>
       <c r="B55" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6921,38 +6921,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127783912</v>
+        <v>127782081</v>
       </c>
       <c r="B56" t="n">
-        <v>105497</v>
+        <v>98467</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654926</v>
+        <v>654807</v>
       </c>
       <c r="R56" t="n">
-        <v>6648527</v>
+        <v>6648524</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7006,7 +7006,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>6 fröställn</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7036,7 +7041,7 @@
         <v>127782436</v>
       </c>
       <c r="B57" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7150,38 +7155,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127782081</v>
+        <v>127783912</v>
       </c>
       <c r="B58" t="n">
-        <v>98459</v>
+        <v>105505</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7190,10 +7195,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654807</v>
+        <v>654926</v>
       </c>
       <c r="R58" t="n">
-        <v>6648524</v>
+        <v>6648527</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7225,7 +7230,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7235,12 +7240,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>6 fröställn</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -2461,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127784378</v>
+        <v>127781998</v>
       </c>
       <c r="B17" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654950</v>
+        <v>654769</v>
       </c>
       <c r="R17" t="n">
-        <v>6648519</v>
+        <v>6648529</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,7 +2546,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,38 +2578,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127781998</v>
+        <v>127781552</v>
       </c>
       <c r="B18" t="n">
-        <v>98467</v>
+        <v>105506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2613,13 +2618,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654769</v>
+        <v>654841</v>
       </c>
       <c r="R18" t="n">
-        <v>6648529</v>
+        <v>6648625</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2648,7 +2653,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,12 +2663,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2690,32 +2690,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127781552</v>
+        <v>127784378</v>
       </c>
       <c r="B19" t="n">
-        <v>105505</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2730,13 +2730,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654841</v>
+        <v>654950</v>
       </c>
       <c r="R19" t="n">
-        <v>6648625</v>
+        <v>6648519</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2805,7 +2805,7 @@
         <v>127782688</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>127781937</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>127781639</v>
       </c>
       <c r="B22" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>127782608</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>127782340</v>
       </c>
       <c r="B24" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,38 +3372,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127783934</v>
+        <v>127783233</v>
       </c>
       <c r="B25" t="n">
-        <v>98467</v>
+        <v>57669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654911</v>
+        <v>654939</v>
       </c>
       <c r="R25" t="n">
-        <v>6648510</v>
+        <v>6648547</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,7 +3457,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I asp. Även bohål st hack.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3484,38 +3489,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127783233</v>
+        <v>127781082</v>
       </c>
       <c r="B26" t="n">
-        <v>57669</v>
+        <v>98468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3524,13 +3529,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654939</v>
+        <v>654826</v>
       </c>
       <c r="R26" t="n">
-        <v>6648547</v>
+        <v>6648657</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3559,7 +3564,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3569,12 +3574,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I asp. Även bohål st hack.</t>
+          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3601,10 +3606,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127781082</v>
+        <v>127783934</v>
       </c>
       <c r="B27" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3641,10 +3646,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654826</v>
+        <v>654911</v>
       </c>
       <c r="R27" t="n">
-        <v>6648657</v>
+        <v>6648510</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
@@ -3676,7 +3681,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3686,12 +3691,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3721,7 +3721,7 @@
         <v>127784226</v>
       </c>
       <c r="B28" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>127781864</v>
       </c>
       <c r="B29" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127782599</v>
+        <v>127780852</v>
       </c>
       <c r="B30" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3987,13 +3987,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654852</v>
+        <v>654829</v>
       </c>
       <c r="R30" t="n">
-        <v>6648592</v>
+        <v>6648641</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4032,7 +4032,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>En fröställning. Utanför, syd om hänsynsyta som snitslat ett fuktstråk med glasbjörk och klibbal på socklar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4059,10 +4064,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127780852</v>
+        <v>127782599</v>
       </c>
       <c r="B31" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4099,13 +4104,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654829</v>
+        <v>654852</v>
       </c>
       <c r="R31" t="n">
-        <v>6648641</v>
+        <v>6648592</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4134,7 +4139,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4144,12 +4149,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>En fröställning. Utanför, syd om hänsynsyta som snitslat ett fuktstråk med glasbjörk och klibbal på socklar.</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4176,10 +4176,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127785581</v>
+        <v>127784696</v>
       </c>
       <c r="B32" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4216,13 +4216,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654763</v>
+        <v>654903</v>
       </c>
       <c r="R32" t="n">
-        <v>6648504</v>
+        <v>6648470</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4291,7 +4291,7 @@
         <v>127781251</v>
       </c>
       <c r="B33" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>127784246</v>
       </c>
       <c r="B34" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127784696</v>
+        <v>127785581</v>
       </c>
       <c r="B35" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654903</v>
+        <v>654763</v>
       </c>
       <c r="R35" t="n">
-        <v>6648470</v>
+        <v>6648504</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4629,10 +4629,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127783185</v>
+        <v>127782582</v>
       </c>
       <c r="B36" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,19 +4658,24 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654900</v>
+        <v>654831</v>
       </c>
       <c r="R36" t="n">
-        <v>6648568</v>
+        <v>6648582</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4699,7 +4704,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4709,12 +4714,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127782582</v>
+        <v>127783185</v>
       </c>
       <c r="B37" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4770,24 +4770,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654831</v>
+        <v>654900</v>
       </c>
       <c r="R37" t="n">
-        <v>6648582</v>
+        <v>6648568</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4816,7 +4811,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4826,7 +4821,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4856,7 +4856,7 @@
         <v>127784050</v>
       </c>
       <c r="B38" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>127782751</v>
       </c>
       <c r="B39" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127782237</v>
+        <v>127781723</v>
       </c>
       <c r="B40" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654811</v>
+        <v>654831</v>
       </c>
       <c r="R40" t="n">
-        <v>6648510</v>
+        <v>6648568</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,10 +5199,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127781898</v>
+        <v>127782237</v>
       </c>
       <c r="B41" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5239,13 +5239,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654812</v>
+        <v>654811</v>
       </c>
       <c r="R41" t="n">
-        <v>6648545</v>
+        <v>6648510</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>7 fröställn inom 3 m radie.</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5319,7 +5319,7 @@
         <v>127781429</v>
       </c>
       <c r="B42" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127781723</v>
+        <v>127782716</v>
       </c>
       <c r="B43" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5473,13 +5473,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654831</v>
+        <v>654873</v>
       </c>
       <c r="R43" t="n">
-        <v>6648568</v>
+        <v>6648615</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
+          <t>Tiotalet bladrosetter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5550,10 +5550,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127782716</v>
+        <v>127783424</v>
       </c>
       <c r="B44" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5590,13 +5590,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654873</v>
+        <v>654926</v>
       </c>
       <c r="R44" t="n">
-        <v>6648615</v>
+        <v>6648527</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5635,12 +5635,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Tiotalet bladrosetter</t>
+          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5667,10 +5667,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127783424</v>
+        <v>127781898</v>
       </c>
       <c r="B45" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654926</v>
+        <v>654812</v>
       </c>
       <c r="R45" t="n">
-        <v>6648527</v>
+        <v>6648545</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
+          <t>7 fröställn inom 3 m radie.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5787,7 +5787,7 @@
         <v>127781122</v>
       </c>
       <c r="B46" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>127782650</v>
       </c>
       <c r="B47" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>127784278</v>
       </c>
       <c r="B48" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>127784001</v>
       </c>
       <c r="B49" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6237,10 +6237,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127780501</v>
+        <v>127782845</v>
       </c>
       <c r="B50" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654892</v>
+        <v>654847</v>
       </c>
       <c r="R50" t="n">
-        <v>6648647</v>
+        <v>6648610</v>
       </c>
       <c r="S50" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6349,10 +6349,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127782845</v>
+        <v>127780501</v>
       </c>
       <c r="B51" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6389,13 +6389,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654847</v>
+        <v>654892</v>
       </c>
       <c r="R51" t="n">
-        <v>6648610</v>
+        <v>6648647</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6585,10 +6585,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127781961</v>
+        <v>127782527</v>
       </c>
       <c r="B53" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6625,13 +6625,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654782</v>
+        <v>654840</v>
       </c>
       <c r="R53" t="n">
-        <v>6648543</v>
+        <v>6648555</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6697,10 +6697,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127782527</v>
+        <v>127781961</v>
       </c>
       <c r="B54" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6737,13 +6737,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654840</v>
+        <v>654782</v>
       </c>
       <c r="R54" t="n">
-        <v>6648555</v>
+        <v>6648543</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6812,7 +6812,7 @@
         <v>127782275</v>
       </c>
       <c r="B55" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6921,38 +6921,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127782081</v>
+        <v>127783912</v>
       </c>
       <c r="B56" t="n">
-        <v>98467</v>
+        <v>105506</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654807</v>
+        <v>654926</v>
       </c>
       <c r="R56" t="n">
-        <v>6648524</v>
+        <v>6648527</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7006,12 +7006,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>6 fröställn</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7038,10 +7033,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127782436</v>
+        <v>127782081</v>
       </c>
       <c r="B57" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7078,13 +7073,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654829</v>
+        <v>654807</v>
       </c>
       <c r="R57" t="n">
-        <v>6648541</v>
+        <v>6648524</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7113,7 +7108,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7123,12 +7118,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>3 fröst.</t>
+          <t>6 fröställn</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7155,38 +7150,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127783912</v>
+        <v>127782436</v>
       </c>
       <c r="B58" t="n">
-        <v>105505</v>
+        <v>98468</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7195,13 +7190,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654926</v>
+        <v>654829</v>
       </c>
       <c r="R58" t="n">
-        <v>6648527</v>
+        <v>6648541</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7230,7 +7225,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7240,7 +7235,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -2461,38 +2461,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127781998</v>
+        <v>127781552</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>105506</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654769</v>
+        <v>654841</v>
       </c>
       <c r="R17" t="n">
-        <v>6648529</v>
+        <v>6648625</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,12 +2546,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2578,32 +2573,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127781552</v>
+        <v>127784378</v>
       </c>
       <c r="B18" t="n">
-        <v>105506</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2618,13 +2613,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654841</v>
+        <v>654950</v>
       </c>
       <c r="R18" t="n">
-        <v>6648625</v>
+        <v>6648519</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2653,7 +2648,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2663,7 +2658,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2690,7 +2685,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127784378</v>
+        <v>127781998</v>
       </c>
       <c r="B19" t="n">
         <v>98468</v>
@@ -2721,7 +2716,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2730,13 +2725,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654950</v>
+        <v>654769</v>
       </c>
       <c r="R19" t="n">
-        <v>6648519</v>
+        <v>6648529</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2765,7 +2760,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,7 +2770,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2802,7 +2802,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127782688</v>
+        <v>127781937</v>
       </c>
       <c r="B20" t="n">
         <v>98468</v>
@@ -2833,7 +2833,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654896</v>
+        <v>654795</v>
       </c>
       <c r="R20" t="n">
-        <v>6648627</v>
+        <v>6648542</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2887,12 +2887,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tiotalet bladrosetter.</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2919,7 +2914,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127781937</v>
+        <v>127782688</v>
       </c>
       <c r="B21" t="n">
         <v>98468</v>
@@ -2950,7 +2945,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2959,13 +2954,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654795</v>
+        <v>654896</v>
       </c>
       <c r="R21" t="n">
-        <v>6648542</v>
+        <v>6648627</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2994,7 +2989,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,7 +2999,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tiotalet bladrosetter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3031,7 +3031,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127781639</v>
+        <v>127782608</v>
       </c>
       <c r="B22" t="n">
         <v>98468</v>
@@ -3071,13 +3071,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654834</v>
+        <v>654882</v>
       </c>
       <c r="R22" t="n">
-        <v>6648587</v>
+        <v>6648586</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3143,7 +3143,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782608</v>
+        <v>127782340</v>
       </c>
       <c r="B23" t="n">
         <v>98468</v>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654882</v>
+        <v>654840</v>
       </c>
       <c r="R23" t="n">
-        <v>6648586</v>
+        <v>6648541</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3228,7 +3228,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>5 fröst.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3255,7 +3260,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127782340</v>
+        <v>127781639</v>
       </c>
       <c r="B24" t="n">
         <v>98468</v>
@@ -3295,13 +3300,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654840</v>
+        <v>654834</v>
       </c>
       <c r="R24" t="n">
-        <v>6648541</v>
+        <v>6648587</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3330,7 +3335,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3340,12 +3345,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>5 fröst.</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4064,7 +4064,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127782599</v>
+        <v>127784246</v>
       </c>
       <c r="B31" t="n">
         <v>98468</v>
@@ -4095,7 +4095,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654852</v>
+        <v>654977</v>
       </c>
       <c r="R31" t="n">
-        <v>6648592</v>
+        <v>6648526</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4176,7 +4176,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127784696</v>
+        <v>127782599</v>
       </c>
       <c r="B32" t="n">
         <v>98468</v>
@@ -4216,13 +4216,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654903</v>
+        <v>654852</v>
       </c>
       <c r="R32" t="n">
-        <v>6648470</v>
+        <v>6648592</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4288,7 +4288,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127781251</v>
+        <v>127784696</v>
       </c>
       <c r="B33" t="n">
         <v>98468</v>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654836</v>
+        <v>654903</v>
       </c>
       <c r="R33" t="n">
-        <v>6648615</v>
+        <v>6648470</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4373,12 +4373,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Sex fröståndare inom 4 m radie. Minst 30 bladrosetter. Ca 20 m syd om hänsynssnitslad yta (fuktstråk m socklar).</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4405,7 +4400,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127784246</v>
+        <v>127781251</v>
       </c>
       <c r="B34" t="n">
         <v>98468</v>
@@ -4436,7 +4431,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4445,10 +4440,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654977</v>
+        <v>654836</v>
       </c>
       <c r="R34" t="n">
-        <v>6648526</v>
+        <v>6648615</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4480,7 +4475,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4490,7 +4485,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Sex fröståndare inom 4 m radie. Minst 30 bladrosetter. Ca 20 m syd om hänsynssnitslad yta (fuktstråk m socklar).</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5082,7 +5082,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127781723</v>
+        <v>127781429</v>
       </c>
       <c r="B40" t="n">
         <v>98468</v>
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654831</v>
+        <v>654841</v>
       </c>
       <c r="R40" t="n">
-        <v>6648568</v>
+        <v>6648625</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
+          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,7 +5199,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127782237</v>
+        <v>127781723</v>
       </c>
       <c r="B41" t="n">
         <v>98468</v>
@@ -5239,13 +5239,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654811</v>
+        <v>654831</v>
       </c>
       <c r="R41" t="n">
-        <v>6648510</v>
+        <v>6648568</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5316,7 +5316,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127781429</v>
+        <v>127782237</v>
       </c>
       <c r="B42" t="n">
         <v>98468</v>
@@ -5356,13 +5356,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654841</v>
+        <v>654811</v>
       </c>
       <c r="R42" t="n">
-        <v>6648625</v>
+        <v>6648510</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5433,7 +5433,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127782716</v>
+        <v>127781898</v>
       </c>
       <c r="B43" t="n">
         <v>98468</v>
@@ -5464,7 +5464,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5473,13 +5473,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654873</v>
+        <v>654812</v>
       </c>
       <c r="R43" t="n">
-        <v>6648615</v>
+        <v>6648545</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Tiotalet bladrosetter</t>
+          <t>7 fröställn inom 3 m radie.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5550,7 +5550,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127783424</v>
+        <v>127782716</v>
       </c>
       <c r="B44" t="n">
         <v>98468</v>
@@ -5590,13 +5590,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654926</v>
+        <v>654873</v>
       </c>
       <c r="R44" t="n">
-        <v>6648527</v>
+        <v>6648615</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5635,12 +5635,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
+          <t>Tiotalet bladrosetter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5667,7 +5667,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127781898</v>
+        <v>127783424</v>
       </c>
       <c r="B45" t="n">
         <v>98468</v>
@@ -5698,7 +5698,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654812</v>
+        <v>654926</v>
       </c>
       <c r="R45" t="n">
-        <v>6648545</v>
+        <v>6648527</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>7 fröställn inom 3 m radie.</t>
+          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5901,7 +5901,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127782650</v>
+        <v>127784278</v>
       </c>
       <c r="B47" t="n">
         <v>98468</v>
@@ -5932,7 +5932,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654890</v>
+        <v>654961</v>
       </c>
       <c r="R47" t="n">
-        <v>6648616</v>
+        <v>6648515</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6013,7 +6013,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127784278</v>
+        <v>127782650</v>
       </c>
       <c r="B48" t="n">
         <v>98468</v>
@@ -6044,7 +6044,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6053,13 +6053,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654961</v>
+        <v>654890</v>
       </c>
       <c r="R48" t="n">
-        <v>6648515</v>
+        <v>6648616</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6585,7 +6585,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127782527</v>
+        <v>127781961</v>
       </c>
       <c r="B53" t="n">
         <v>98468</v>
@@ -6625,13 +6625,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654840</v>
+        <v>654782</v>
       </c>
       <c r="R53" t="n">
-        <v>6648555</v>
+        <v>6648543</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6697,7 +6697,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127781961</v>
+        <v>127782527</v>
       </c>
       <c r="B54" t="n">
         <v>98468</v>
@@ -6737,13 +6737,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654782</v>
+        <v>654840</v>
       </c>
       <c r="R54" t="n">
-        <v>6648543</v>
+        <v>6648555</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6921,38 +6921,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127783912</v>
+        <v>127782436</v>
       </c>
       <c r="B56" t="n">
-        <v>105506</v>
+        <v>98468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654926</v>
+        <v>654829</v>
       </c>
       <c r="R56" t="n">
-        <v>6648527</v>
+        <v>6648541</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7006,7 +7006,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7033,38 +7038,38 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127782081</v>
+        <v>127783912</v>
       </c>
       <c r="B57" t="n">
-        <v>98468</v>
+        <v>105506</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7073,10 +7078,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654807</v>
+        <v>654926</v>
       </c>
       <c r="R57" t="n">
-        <v>6648524</v>
+        <v>6648527</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7108,7 +7113,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7118,12 +7123,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>6 fröställn</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7150,7 +7150,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127782436</v>
+        <v>127782081</v>
       </c>
       <c r="B58" t="n">
         <v>98468</v>
@@ -7190,13 +7190,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654829</v>
+        <v>654807</v>
       </c>
       <c r="R58" t="n">
-        <v>6648541</v>
+        <v>6648524</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7235,12 +7235,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>3 fröst.</t>
+          <t>6 fröställn</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -2461,38 +2461,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127781552</v>
+        <v>127781998</v>
       </c>
       <c r="B17" t="n">
-        <v>105506</v>
+        <v>98469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654841</v>
+        <v>654769</v>
       </c>
       <c r="R17" t="n">
-        <v>6648625</v>
+        <v>6648529</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,7 +2546,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,32 +2578,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127784378</v>
+        <v>127781552</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>105507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2613,13 +2618,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654950</v>
+        <v>654841</v>
       </c>
       <c r="R18" t="n">
-        <v>6648519</v>
+        <v>6648625</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2648,7 +2653,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,7 +2663,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2685,10 +2690,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127781998</v>
+        <v>127784378</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2716,7 +2721,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2725,13 +2730,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654769</v>
+        <v>654950</v>
       </c>
       <c r="R19" t="n">
-        <v>6648529</v>
+        <v>6648519</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2760,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2770,12 +2775,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2802,10 +2802,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127781937</v>
+        <v>127782688</v>
       </c>
       <c r="B20" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654795</v>
+        <v>654896</v>
       </c>
       <c r="R20" t="n">
-        <v>6648542</v>
+        <v>6648627</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2887,7 +2887,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tiotalet bladrosetter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2914,10 +2919,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127782688</v>
+        <v>127781937</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2950,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2954,13 +2959,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654896</v>
+        <v>654795</v>
       </c>
       <c r="R21" t="n">
-        <v>6648627</v>
+        <v>6648542</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2989,7 +2994,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2999,12 +3004,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tiotalet bladrosetter.</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3031,10 +3031,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127782608</v>
+        <v>127782340</v>
       </c>
       <c r="B22" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654882</v>
+        <v>654840</v>
       </c>
       <c r="R22" t="n">
-        <v>6648586</v>
+        <v>6648541</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3116,7 +3116,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 fröst.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3143,10 +3148,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782340</v>
+        <v>127782608</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,10 +3188,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654840</v>
+        <v>654882</v>
       </c>
       <c r="R23" t="n">
-        <v>6648541</v>
+        <v>6648586</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3218,7 +3223,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3228,12 +3233,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>5 fröst.</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3263,7 +3263,7 @@
         <v>127781639</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,38 +3372,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127783233</v>
+        <v>127783934</v>
       </c>
       <c r="B25" t="n">
-        <v>57669</v>
+        <v>98469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654939</v>
+        <v>654911</v>
       </c>
       <c r="R25" t="n">
-        <v>6648547</v>
+        <v>6648510</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,12 +3457,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:52</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>I asp. Även bohål st hack.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3492,7 +3487,7 @@
         <v>127781082</v>
       </c>
       <c r="B26" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3606,38 +3601,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127783934</v>
+        <v>127783233</v>
       </c>
       <c r="B27" t="n">
-        <v>98468</v>
+        <v>57669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3646,13 +3641,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654911</v>
+        <v>654939</v>
       </c>
       <c r="R27" t="n">
-        <v>6648510</v>
+        <v>6648547</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3681,7 +3676,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3691,7 +3686,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>I asp. Även bohål st hack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3721,7 +3721,7 @@
         <v>127784226</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>127781864</v>
       </c>
       <c r="B29" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>127780852</v>
       </c>
       <c r="B30" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127784246</v>
+        <v>127785581</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654977</v>
+        <v>654763</v>
       </c>
       <c r="R31" t="n">
-        <v>6648526</v>
+        <v>6648504</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4179,7 +4179,7 @@
         <v>127782599</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4288,10 +4288,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127784696</v>
+        <v>127781251</v>
       </c>
       <c r="B33" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654903</v>
+        <v>654836</v>
       </c>
       <c r="R33" t="n">
-        <v>6648470</v>
+        <v>6648615</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4373,7 +4373,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Sex fröståndare inom 4 m radie. Minst 30 bladrosetter. Ca 20 m syd om hänsynssnitslad yta (fuktstråk m socklar).</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4400,10 +4405,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127781251</v>
+        <v>127784246</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4431,7 +4436,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4440,10 +4445,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654836</v>
+        <v>654977</v>
       </c>
       <c r="R34" t="n">
-        <v>6648615</v>
+        <v>6648526</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4475,7 +4480,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4485,12 +4490,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Sex fröståndare inom 4 m radie. Minst 30 bladrosetter. Ca 20 m syd om hänsynssnitslad yta (fuktstråk m socklar).</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4517,10 +4517,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127785581</v>
+        <v>127784696</v>
       </c>
       <c r="B35" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654763</v>
+        <v>654903</v>
       </c>
       <c r="R35" t="n">
-        <v>6648504</v>
+        <v>6648470</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4629,10 +4629,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127782582</v>
+        <v>127783185</v>
       </c>
       <c r="B36" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,24 +4658,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654831</v>
+        <v>654900</v>
       </c>
       <c r="R36" t="n">
-        <v>6648582</v>
+        <v>6648568</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4704,7 +4699,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4714,7 +4709,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127783185</v>
+        <v>127782582</v>
       </c>
       <c r="B37" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4770,19 +4770,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654900</v>
+        <v>654831</v>
       </c>
       <c r="R37" t="n">
-        <v>6648568</v>
+        <v>6648582</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4811,7 +4816,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4821,12 +4826,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4856,7 +4856,7 @@
         <v>127784050</v>
       </c>
       <c r="B38" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>127782751</v>
       </c>
       <c r="B39" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127781429</v>
+        <v>127782237</v>
       </c>
       <c r="B40" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654841</v>
+        <v>654811</v>
       </c>
       <c r="R40" t="n">
-        <v>6648625</v>
+        <v>6648510</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,10 +5199,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127781723</v>
+        <v>127781898</v>
       </c>
       <c r="B41" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654831</v>
+        <v>654812</v>
       </c>
       <c r="R41" t="n">
-        <v>6648568</v>
+        <v>6648545</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
+          <t>7 fröställn inom 3 m radie.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5316,10 +5316,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127782237</v>
+        <v>127781723</v>
       </c>
       <c r="B42" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5356,13 +5356,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654811</v>
+        <v>654831</v>
       </c>
       <c r="R42" t="n">
-        <v>6648510</v>
+        <v>6648568</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127781898</v>
+        <v>127782716</v>
       </c>
       <c r="B43" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5473,13 +5473,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654812</v>
+        <v>654873</v>
       </c>
       <c r="R43" t="n">
-        <v>6648545</v>
+        <v>6648615</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>7 fröställn inom 3 m radie.</t>
+          <t>Tiotalet bladrosetter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5550,10 +5550,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127782716</v>
+        <v>127783424</v>
       </c>
       <c r="B44" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5590,13 +5590,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654873</v>
+        <v>654926</v>
       </c>
       <c r="R44" t="n">
-        <v>6648615</v>
+        <v>6648527</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5635,12 +5635,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Tiotalet bladrosetter</t>
+          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5667,10 +5667,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127783424</v>
+        <v>127781429</v>
       </c>
       <c r="B45" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654926</v>
+        <v>654841</v>
       </c>
       <c r="R45" t="n">
-        <v>6648527</v>
+        <v>6648625</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
+          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5787,7 +5787,7 @@
         <v>127781122</v>
       </c>
       <c r="B46" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>127784278</v>
       </c>
       <c r="B47" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127782650</v>
+        <v>127784001</v>
       </c>
       <c r="B48" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654890</v>
+        <v>654913</v>
       </c>
       <c r="R48" t="n">
-        <v>6648616</v>
+        <v>6648493</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6125,10 +6125,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127784001</v>
+        <v>127782650</v>
       </c>
       <c r="B49" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6165,10 +6165,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654913</v>
+        <v>654890</v>
       </c>
       <c r="R49" t="n">
-        <v>6648493</v>
+        <v>6648616</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6237,10 +6237,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127782845</v>
+        <v>127780501</v>
       </c>
       <c r="B50" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654847</v>
+        <v>654892</v>
       </c>
       <c r="R50" t="n">
-        <v>6648610</v>
+        <v>6648647</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6349,10 +6349,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127780501</v>
+        <v>127782845</v>
       </c>
       <c r="B51" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6389,13 +6389,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654892</v>
+        <v>654847</v>
       </c>
       <c r="R51" t="n">
-        <v>6648647</v>
+        <v>6648610</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6588,7 +6588,7 @@
         <v>127781961</v>
       </c>
       <c r="B53" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>127782527</v>
       </c>
       <c r="B54" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>127782275</v>
       </c>
       <c r="B55" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6921,10 +6921,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127782436</v>
+        <v>127782081</v>
       </c>
       <c r="B56" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654829</v>
+        <v>654807</v>
       </c>
       <c r="R56" t="n">
-        <v>6648541</v>
+        <v>6648524</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7006,12 +7006,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>3 fröst.</t>
+          <t>6 fröställn</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7038,38 +7038,38 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127783912</v>
+        <v>127782436</v>
       </c>
       <c r="B57" t="n">
-        <v>105506</v>
+        <v>98469</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7078,13 +7078,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654926</v>
+        <v>654829</v>
       </c>
       <c r="R57" t="n">
-        <v>6648527</v>
+        <v>6648541</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7123,7 +7123,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7150,38 +7155,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127782081</v>
+        <v>127783912</v>
       </c>
       <c r="B58" t="n">
-        <v>98468</v>
+        <v>105507</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7190,10 +7195,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654807</v>
+        <v>654926</v>
       </c>
       <c r="R58" t="n">
-        <v>6648524</v>
+        <v>6648527</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7225,7 +7230,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7235,12 +7240,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>6 fröställn</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -2461,38 +2461,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127781998</v>
+        <v>127781552</v>
       </c>
       <c r="B17" t="n">
-        <v>98469</v>
+        <v>105508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654769</v>
+        <v>654841</v>
       </c>
       <c r="R17" t="n">
-        <v>6648529</v>
+        <v>6648625</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,12 +2546,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2578,32 +2573,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127781552</v>
+        <v>127784378</v>
       </c>
       <c r="B18" t="n">
-        <v>105507</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2618,13 +2613,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654841</v>
+        <v>654950</v>
       </c>
       <c r="R18" t="n">
-        <v>6648625</v>
+        <v>6648519</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2653,7 +2648,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2663,7 +2658,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2690,10 +2685,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127784378</v>
+        <v>127781998</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2716,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2730,13 +2725,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654950</v>
+        <v>654769</v>
       </c>
       <c r="R19" t="n">
-        <v>6648519</v>
+        <v>6648529</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2765,7 +2760,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,7 +2770,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2802,10 +2802,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127782688</v>
+        <v>127781937</v>
       </c>
       <c r="B20" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654896</v>
+        <v>654795</v>
       </c>
       <c r="R20" t="n">
-        <v>6648627</v>
+        <v>6648542</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2887,12 +2887,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tiotalet bladrosetter.</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2919,10 +2914,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127781937</v>
+        <v>127782688</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2950,7 +2945,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2959,13 +2954,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654795</v>
+        <v>654896</v>
       </c>
       <c r="R21" t="n">
-        <v>6648542</v>
+        <v>6648627</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2994,7 +2989,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,7 +2999,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tiotalet bladrosetter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3031,10 +3031,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127782340</v>
+        <v>127781639</v>
       </c>
       <c r="B22" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3071,13 +3071,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654840</v>
+        <v>654834</v>
       </c>
       <c r="R22" t="n">
-        <v>6648541</v>
+        <v>6648587</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3116,12 +3116,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>5 fröst.</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3151,7 +3146,7 @@
         <v>127782608</v>
       </c>
       <c r="B23" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3260,10 +3255,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127781639</v>
+        <v>127782340</v>
       </c>
       <c r="B24" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3300,13 +3295,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654834</v>
+        <v>654840</v>
       </c>
       <c r="R24" t="n">
-        <v>6648587</v>
+        <v>6648541</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3335,7 +3330,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3345,7 +3340,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>5 fröst.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3372,38 +3372,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127783934</v>
+        <v>127783233</v>
       </c>
       <c r="B25" t="n">
-        <v>98469</v>
+        <v>57669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654911</v>
+        <v>654939</v>
       </c>
       <c r="R25" t="n">
-        <v>6648510</v>
+        <v>6648547</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,7 +3457,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I asp. Även bohål st hack.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3487,7 +3492,7 @@
         <v>127781082</v>
       </c>
       <c r="B26" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,38 +3606,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127783233</v>
+        <v>127783934</v>
       </c>
       <c r="B27" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3641,13 +3646,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654939</v>
+        <v>654911</v>
       </c>
       <c r="R27" t="n">
-        <v>6648547</v>
+        <v>6648510</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3676,7 +3681,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3686,12 +3691,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:52</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>I asp. Även bohål st hack.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3721,7 +3721,7 @@
         <v>127784226</v>
       </c>
       <c r="B28" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>127781864</v>
       </c>
       <c r="B29" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>127780852</v>
       </c>
       <c r="B30" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127785581</v>
+        <v>127782599</v>
       </c>
       <c r="B31" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654763</v>
+        <v>654852</v>
       </c>
       <c r="R31" t="n">
-        <v>6648504</v>
+        <v>6648592</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4176,10 +4176,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127782599</v>
+        <v>127784696</v>
       </c>
       <c r="B32" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4216,13 +4216,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654852</v>
+        <v>654903</v>
       </c>
       <c r="R32" t="n">
-        <v>6648592</v>
+        <v>6648470</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4291,7 +4291,7 @@
         <v>127781251</v>
       </c>
       <c r="B33" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>127784246</v>
       </c>
       <c r="B34" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127784696</v>
+        <v>127785581</v>
       </c>
       <c r="B35" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654903</v>
+        <v>654763</v>
       </c>
       <c r="R35" t="n">
-        <v>6648470</v>
+        <v>6648504</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4629,10 +4629,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127783185</v>
+        <v>127782582</v>
       </c>
       <c r="B36" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,19 +4658,24 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654900</v>
+        <v>654831</v>
       </c>
       <c r="R36" t="n">
-        <v>6648568</v>
+        <v>6648582</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4699,7 +4704,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4709,12 +4714,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127782582</v>
+        <v>127783185</v>
       </c>
       <c r="B37" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4770,24 +4770,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654831</v>
+        <v>654900</v>
       </c>
       <c r="R37" t="n">
-        <v>6648582</v>
+        <v>6648568</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4816,7 +4811,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4826,7 +4821,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4856,7 +4856,7 @@
         <v>127784050</v>
       </c>
       <c r="B38" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>127782751</v>
       </c>
       <c r="B39" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127782237</v>
+        <v>127781723</v>
       </c>
       <c r="B40" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654811</v>
+        <v>654831</v>
       </c>
       <c r="R40" t="n">
-        <v>6648510</v>
+        <v>6648568</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,10 +5199,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127781898</v>
+        <v>127782237</v>
       </c>
       <c r="B41" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5239,13 +5239,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654812</v>
+        <v>654811</v>
       </c>
       <c r="R41" t="n">
-        <v>6648545</v>
+        <v>6648510</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>7 fröställn inom 3 m radie.</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5316,10 +5316,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127781723</v>
+        <v>127781429</v>
       </c>
       <c r="B42" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5356,13 +5356,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654831</v>
+        <v>654841</v>
       </c>
       <c r="R42" t="n">
-        <v>6648568</v>
+        <v>6648625</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
+          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127782716</v>
+        <v>127781898</v>
       </c>
       <c r="B43" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5473,13 +5473,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654873</v>
+        <v>654812</v>
       </c>
       <c r="R43" t="n">
-        <v>6648615</v>
+        <v>6648545</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Tiotalet bladrosetter</t>
+          <t>7 fröställn inom 3 m radie.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5550,10 +5550,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127783424</v>
+        <v>127782716</v>
       </c>
       <c r="B44" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5590,13 +5590,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654926</v>
+        <v>654873</v>
       </c>
       <c r="R44" t="n">
-        <v>6648527</v>
+        <v>6648615</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5635,12 +5635,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
+          <t>Tiotalet bladrosetter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5667,10 +5667,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127781429</v>
+        <v>127783424</v>
       </c>
       <c r="B45" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654841</v>
+        <v>654926</v>
       </c>
       <c r="R45" t="n">
-        <v>6648625</v>
+        <v>6648527</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
+          <t>Ca 15 m syd, utanför hänsynsyta som i huvudsak utgörs av trädlös renlavshällmarksyta.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5787,7 +5787,7 @@
         <v>127781122</v>
       </c>
       <c r="B46" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127784278</v>
+        <v>127782650</v>
       </c>
       <c r="B47" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654961</v>
+        <v>654890</v>
       </c>
       <c r="R47" t="n">
-        <v>6648515</v>
+        <v>6648616</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6013,10 +6013,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127784001</v>
+        <v>127784278</v>
       </c>
       <c r="B48" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6053,13 +6053,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654913</v>
+        <v>654961</v>
       </c>
       <c r="R48" t="n">
-        <v>6648493</v>
+        <v>6648515</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6125,10 +6125,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127782650</v>
+        <v>127784001</v>
       </c>
       <c r="B49" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6165,10 +6165,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654890</v>
+        <v>654913</v>
       </c>
       <c r="R49" t="n">
-        <v>6648616</v>
+        <v>6648493</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6237,10 +6237,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127780501</v>
+        <v>127782845</v>
       </c>
       <c r="B50" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654892</v>
+        <v>654847</v>
       </c>
       <c r="R50" t="n">
-        <v>6648647</v>
+        <v>6648610</v>
       </c>
       <c r="S50" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6349,10 +6349,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127782845</v>
+        <v>127780501</v>
       </c>
       <c r="B51" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6389,13 +6389,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654847</v>
+        <v>654892</v>
       </c>
       <c r="R51" t="n">
-        <v>6648610</v>
+        <v>6648647</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6588,7 +6588,7 @@
         <v>127781961</v>
       </c>
       <c r="B53" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>127782527</v>
       </c>
       <c r="B54" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>127782275</v>
       </c>
       <c r="B55" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6921,38 +6921,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127782081</v>
+        <v>127783912</v>
       </c>
       <c r="B56" t="n">
-        <v>98469</v>
+        <v>105508</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654807</v>
+        <v>654926</v>
       </c>
       <c r="R56" t="n">
-        <v>6648524</v>
+        <v>6648527</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7006,12 +7006,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>6 fröställn</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7041,7 +7036,7 @@
         <v>127782436</v>
       </c>
       <c r="B57" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7155,38 +7150,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127783912</v>
+        <v>127782081</v>
       </c>
       <c r="B58" t="n">
-        <v>105507</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7195,10 +7190,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654926</v>
+        <v>654807</v>
       </c>
       <c r="R58" t="n">
-        <v>6648527</v>
+        <v>6648524</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7230,7 +7225,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7240,7 +7235,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>6 fröställn</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -2573,7 +2573,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127784378</v>
+        <v>127781998</v>
       </c>
       <c r="B18" t="n">
         <v>98470</v>
@@ -2604,7 +2604,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654950</v>
+        <v>654769</v>
       </c>
       <c r="R18" t="n">
-        <v>6648519</v>
+        <v>6648529</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,7 +2658,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2685,7 +2690,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127781998</v>
+        <v>127784378</v>
       </c>
       <c r="B19" t="n">
         <v>98470</v>
@@ -2716,7 +2721,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2725,13 +2730,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654769</v>
+        <v>654950</v>
       </c>
       <c r="R19" t="n">
-        <v>6648529</v>
+        <v>6648519</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2760,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2770,12 +2775,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4405,7 +4405,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127784246</v>
+        <v>127785581</v>
       </c>
       <c r="B34" t="n">
         <v>98470</v>
@@ -4436,7 +4436,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654977</v>
+        <v>654763</v>
       </c>
       <c r="R34" t="n">
-        <v>6648526</v>
+        <v>6648504</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4517,7 +4517,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127785581</v>
+        <v>127784246</v>
       </c>
       <c r="B35" t="n">
         <v>98470</v>
@@ -4548,7 +4548,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654763</v>
+        <v>654977</v>
       </c>
       <c r="R35" t="n">
-        <v>6648504</v>
+        <v>6648526</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4853,7 +4853,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127784050</v>
+        <v>127782751</v>
       </c>
       <c r="B38" t="n">
         <v>98470</v>
@@ -4893,13 +4893,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654933</v>
+        <v>654873</v>
       </c>
       <c r="R38" t="n">
-        <v>6648492</v>
+        <v>6648648</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4938,7 +4938,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 25 bladrosetter.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4965,7 +4970,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127782751</v>
+        <v>127784050</v>
       </c>
       <c r="B39" t="n">
         <v>98470</v>
@@ -5005,13 +5010,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654873</v>
+        <v>654933</v>
       </c>
       <c r="R39" t="n">
-        <v>6648648</v>
+        <v>6648492</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5040,7 +5045,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5050,12 +5055,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 25 bladrosetter.</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6921,38 +6921,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127783912</v>
+        <v>127782436</v>
       </c>
       <c r="B56" t="n">
-        <v>105508</v>
+        <v>98470</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654926</v>
+        <v>654829</v>
       </c>
       <c r="R56" t="n">
-        <v>6648527</v>
+        <v>6648541</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7006,7 +7006,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7033,7 +7038,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127782436</v>
+        <v>127782081</v>
       </c>
       <c r="B57" t="n">
         <v>98470</v>
@@ -7073,13 +7078,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654829</v>
+        <v>654807</v>
       </c>
       <c r="R57" t="n">
-        <v>6648541</v>
+        <v>6648524</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7108,7 +7113,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7118,12 +7123,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>3 fröst.</t>
+          <t>6 fröställn</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7150,38 +7155,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127782081</v>
+        <v>127783912</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>105508</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7190,10 +7195,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654807</v>
+        <v>654926</v>
       </c>
       <c r="R58" t="n">
-        <v>6648524</v>
+        <v>6648527</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7225,7 +7230,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7235,12 +7240,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>6 fröställn</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -4405,7 +4405,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127785581</v>
+        <v>127784246</v>
       </c>
       <c r="B34" t="n">
         <v>98470</v>
@@ -4436,7 +4436,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654763</v>
+        <v>654977</v>
       </c>
       <c r="R34" t="n">
-        <v>6648504</v>
+        <v>6648526</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4517,7 +4517,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127784246</v>
+        <v>127785581</v>
       </c>
       <c r="B35" t="n">
         <v>98470</v>
@@ -4548,7 +4548,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654977</v>
+        <v>654763</v>
       </c>
       <c r="R35" t="n">
-        <v>6648526</v>
+        <v>6648504</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -6461,60 +6461,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127785899</v>
+        <v>127781961</v>
       </c>
       <c r="B52" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654819</v>
+        <v>654782</v>
       </c>
       <c r="R52" t="n">
-        <v>6648643</v>
+        <v>6648543</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6543,7 +6536,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6553,12 +6546,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6585,7 +6573,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127781961</v>
+        <v>127782527</v>
       </c>
       <c r="B53" t="n">
         <v>98470</v>
@@ -6625,13 +6613,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654782</v>
+        <v>654840</v>
       </c>
       <c r="R53" t="n">
-        <v>6648543</v>
+        <v>6648555</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6660,7 +6648,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6670,7 +6658,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6697,53 +6685,60 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127782527</v>
+        <v>127785899</v>
       </c>
       <c r="B54" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654840</v>
+        <v>654819</v>
       </c>
       <c r="R54" t="n">
-        <v>6648555</v>
+        <v>6648643</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6772,7 +6767,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6782,7 +6777,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6921,38 +6921,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127782436</v>
+        <v>127783912</v>
       </c>
       <c r="B56" t="n">
-        <v>98470</v>
+        <v>105508</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654829</v>
+        <v>654926</v>
       </c>
       <c r="R56" t="n">
-        <v>6648541</v>
+        <v>6648527</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7006,12 +7006,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:05</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7038,7 +7033,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127782081</v>
+        <v>127782436</v>
       </c>
       <c r="B57" t="n">
         <v>98470</v>
@@ -7078,13 +7073,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654807</v>
+        <v>654829</v>
       </c>
       <c r="R57" t="n">
-        <v>6648524</v>
+        <v>6648541</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7113,7 +7108,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7123,12 +7118,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>6 fröställn</t>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7155,38 +7150,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127783912</v>
+        <v>127782081</v>
       </c>
       <c r="B58" t="n">
-        <v>105508</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7195,10 +7190,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654926</v>
+        <v>654807</v>
       </c>
       <c r="R58" t="n">
-        <v>6648527</v>
+        <v>6648524</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7230,7 +7225,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7240,7 +7235,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>6 fröställn</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -2573,7 +2573,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127781998</v>
+        <v>127784378</v>
       </c>
       <c r="B18" t="n">
         <v>98470</v>
@@ -2604,7 +2604,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654769</v>
+        <v>654950</v>
       </c>
       <c r="R18" t="n">
-        <v>6648529</v>
+        <v>6648519</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,12 +2658,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2690,7 +2685,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127784378</v>
+        <v>127781998</v>
       </c>
       <c r="B19" t="n">
         <v>98470</v>
@@ -2721,7 +2716,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2730,13 +2725,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654950</v>
+        <v>654769</v>
       </c>
       <c r="R19" t="n">
-        <v>6648519</v>
+        <v>6648529</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2765,7 +2760,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,7 +2770,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4405,7 +4405,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127784246</v>
+        <v>127785581</v>
       </c>
       <c r="B34" t="n">
         <v>98470</v>
@@ -4436,7 +4436,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654977</v>
+        <v>654763</v>
       </c>
       <c r="R34" t="n">
-        <v>6648526</v>
+        <v>6648504</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4517,7 +4517,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127785581</v>
+        <v>127784246</v>
       </c>
       <c r="B35" t="n">
         <v>98470</v>
@@ -4548,7 +4548,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654763</v>
+        <v>654977</v>
       </c>
       <c r="R35" t="n">
-        <v>6648504</v>
+        <v>6648526</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -6921,38 +6921,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127783912</v>
+        <v>127782436</v>
       </c>
       <c r="B56" t="n">
-        <v>105508</v>
+        <v>98470</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654926</v>
+        <v>654829</v>
       </c>
       <c r="R56" t="n">
-        <v>6648527</v>
+        <v>6648541</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7006,7 +7006,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7033,7 +7038,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127782436</v>
+        <v>127782081</v>
       </c>
       <c r="B57" t="n">
         <v>98470</v>
@@ -7073,13 +7078,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654829</v>
+        <v>654807</v>
       </c>
       <c r="R57" t="n">
-        <v>6648541</v>
+        <v>6648524</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7108,7 +7113,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7118,12 +7123,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>3 fröst.</t>
+          <t>6 fröställn</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7150,38 +7155,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127782081</v>
+        <v>127783912</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>105508</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7190,10 +7195,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654807</v>
+        <v>654926</v>
       </c>
       <c r="R58" t="n">
-        <v>6648524</v>
+        <v>6648527</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7225,7 +7230,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7235,12 +7240,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>6 fröställn</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -2573,7 +2573,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127784378</v>
+        <v>127781998</v>
       </c>
       <c r="B18" t="n">
         <v>98470</v>
@@ -2604,7 +2604,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654950</v>
+        <v>654769</v>
       </c>
       <c r="R18" t="n">
-        <v>6648519</v>
+        <v>6648529</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,7 +2658,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2685,7 +2690,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127781998</v>
+        <v>127784378</v>
       </c>
       <c r="B19" t="n">
         <v>98470</v>
@@ -2716,7 +2721,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2725,13 +2730,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654769</v>
+        <v>654950</v>
       </c>
       <c r="R19" t="n">
-        <v>6648529</v>
+        <v>6648519</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2760,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2770,12 +2775,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3372,38 +3372,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127783233</v>
+        <v>127781082</v>
       </c>
       <c r="B25" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654939</v>
+        <v>654826</v>
       </c>
       <c r="R25" t="n">
-        <v>6648547</v>
+        <v>6648657</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I asp. Även bohål st hack.</t>
+          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3489,7 +3489,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127781082</v>
+        <v>127783934</v>
       </c>
       <c r="B26" t="n">
         <v>98470</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654826</v>
+        <v>654911</v>
       </c>
       <c r="R26" t="n">
-        <v>6648657</v>
+        <v>6648510</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3574,12 +3574,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3606,38 +3601,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127783934</v>
+        <v>127783233</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3646,13 +3641,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654911</v>
+        <v>654939</v>
       </c>
       <c r="R27" t="n">
-        <v>6648510</v>
+        <v>6648547</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3681,7 +3676,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3691,7 +3686,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>I asp. Även bohål st hack.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -4405,7 +4405,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127785581</v>
+        <v>127784246</v>
       </c>
       <c r="B34" t="n">
         <v>98470</v>
@@ -4436,7 +4436,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654763</v>
+        <v>654977</v>
       </c>
       <c r="R34" t="n">
-        <v>6648504</v>
+        <v>6648526</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4517,7 +4517,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127784246</v>
+        <v>127785581</v>
       </c>
       <c r="B35" t="n">
         <v>98470</v>
@@ -4548,7 +4548,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654977</v>
+        <v>654763</v>
       </c>
       <c r="R35" t="n">
-        <v>6648526</v>
+        <v>6648504</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -6921,38 +6921,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127782436</v>
+        <v>127783912</v>
       </c>
       <c r="B56" t="n">
-        <v>98470</v>
+        <v>105508</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654829</v>
+        <v>654926</v>
       </c>
       <c r="R56" t="n">
-        <v>6648541</v>
+        <v>6648527</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7006,12 +7006,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:05</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7038,7 +7033,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127782081</v>
+        <v>127782436</v>
       </c>
       <c r="B57" t="n">
         <v>98470</v>
@@ -7078,13 +7073,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654807</v>
+        <v>654829</v>
       </c>
       <c r="R57" t="n">
-        <v>6648524</v>
+        <v>6648541</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7113,7 +7108,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7123,12 +7118,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>6 fröställn</t>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7155,38 +7150,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127783912</v>
+        <v>127782081</v>
       </c>
       <c r="B58" t="n">
-        <v>105508</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7195,10 +7190,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654926</v>
+        <v>654807</v>
       </c>
       <c r="R58" t="n">
-        <v>6648527</v>
+        <v>6648524</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7230,7 +7225,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7240,7 +7235,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>6 fröställn</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -2573,7 +2573,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127781998</v>
+        <v>127784378</v>
       </c>
       <c r="B18" t="n">
         <v>98470</v>
@@ -2604,7 +2604,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654769</v>
+        <v>654950</v>
       </c>
       <c r="R18" t="n">
-        <v>6648529</v>
+        <v>6648519</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,12 +2658,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2690,7 +2685,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127784378</v>
+        <v>127781998</v>
       </c>
       <c r="B19" t="n">
         <v>98470</v>
@@ -2721,7 +2716,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2730,13 +2725,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654950</v>
+        <v>654769</v>
       </c>
       <c r="R19" t="n">
-        <v>6648519</v>
+        <v>6648529</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2765,7 +2760,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,7 +2770,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3372,38 +3372,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127781082</v>
+        <v>127783233</v>
       </c>
       <c r="B25" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654826</v>
+        <v>654939</v>
       </c>
       <c r="R25" t="n">
-        <v>6648657</v>
+        <v>6648547</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
+          <t>I asp. Även bohål st hack.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3489,7 +3489,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127783934</v>
+        <v>127781082</v>
       </c>
       <c r="B26" t="n">
         <v>98470</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654911</v>
+        <v>654826</v>
       </c>
       <c r="R26" t="n">
-        <v>6648510</v>
+        <v>6648657</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3574,7 +3574,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3601,38 +3606,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127783233</v>
+        <v>127783934</v>
       </c>
       <c r="B27" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3641,13 +3646,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654939</v>
+        <v>654911</v>
       </c>
       <c r="R27" t="n">
-        <v>6648547</v>
+        <v>6648510</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3676,7 +3681,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3686,12 +3691,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:52</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>I asp. Även bohål st hack.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -6921,38 +6921,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127783912</v>
+        <v>127782436</v>
       </c>
       <c r="B56" t="n">
-        <v>105508</v>
+        <v>98470</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654926</v>
+        <v>654829</v>
       </c>
       <c r="R56" t="n">
-        <v>6648527</v>
+        <v>6648541</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7006,7 +7006,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7033,7 +7038,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127782436</v>
+        <v>127782081</v>
       </c>
       <c r="B57" t="n">
         <v>98470</v>
@@ -7073,13 +7078,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654829</v>
+        <v>654807</v>
       </c>
       <c r="R57" t="n">
-        <v>6648541</v>
+        <v>6648524</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7108,7 +7113,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7118,12 +7123,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>3 fröst.</t>
+          <t>6 fröställn</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7150,38 +7155,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127782081</v>
+        <v>127783912</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>105508</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7190,10 +7195,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654807</v>
+        <v>654926</v>
       </c>
       <c r="R58" t="n">
-        <v>6648524</v>
+        <v>6648527</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7225,7 +7230,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7235,12 +7240,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>6 fröställn</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -2573,7 +2573,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127784378</v>
+        <v>127781998</v>
       </c>
       <c r="B18" t="n">
         <v>98470</v>
@@ -2604,7 +2604,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654950</v>
+        <v>654769</v>
       </c>
       <c r="R18" t="n">
-        <v>6648519</v>
+        <v>6648529</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,7 +2658,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2685,7 +2690,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127781998</v>
+        <v>127784378</v>
       </c>
       <c r="B19" t="n">
         <v>98470</v>
@@ -2716,7 +2721,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2725,13 +2730,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654769</v>
+        <v>654950</v>
       </c>
       <c r="R19" t="n">
-        <v>6648529</v>
+        <v>6648519</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2760,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2770,12 +2775,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4405,7 +4405,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127784246</v>
+        <v>127785581</v>
       </c>
       <c r="B34" t="n">
         <v>98470</v>
@@ -4436,7 +4436,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654977</v>
+        <v>654763</v>
       </c>
       <c r="R34" t="n">
-        <v>6648526</v>
+        <v>6648504</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4517,7 +4517,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127785581</v>
+        <v>127784246</v>
       </c>
       <c r="B35" t="n">
         <v>98470</v>
@@ -4548,7 +4548,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654763</v>
+        <v>654977</v>
       </c>
       <c r="R35" t="n">
-        <v>6648504</v>
+        <v>6648526</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -6461,53 +6461,60 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127781961</v>
+        <v>127785899</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654782</v>
+        <v>654819</v>
       </c>
       <c r="R52" t="n">
-        <v>6648543</v>
+        <v>6648643</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6536,7 +6543,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6546,7 +6553,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6573,7 +6585,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127782527</v>
+        <v>127781961</v>
       </c>
       <c r="B53" t="n">
         <v>98470</v>
@@ -6613,13 +6625,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654840</v>
+        <v>654782</v>
       </c>
       <c r="R53" t="n">
-        <v>6648555</v>
+        <v>6648543</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6648,7 +6660,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6658,7 +6670,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6685,60 +6697,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127785899</v>
+        <v>127782527</v>
       </c>
       <c r="B54" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654819</v>
+        <v>654840</v>
       </c>
       <c r="R54" t="n">
-        <v>6648643</v>
+        <v>6648555</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6767,7 +6772,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6777,12 +6782,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -2461,32 +2461,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127781552</v>
+        <v>127784378</v>
       </c>
       <c r="B17" t="n">
-        <v>105508</v>
+        <v>98478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654841</v>
+        <v>654950</v>
       </c>
       <c r="R17" t="n">
-        <v>6648625</v>
+        <v>6648519</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2576,7 +2576,7 @@
         <v>127781998</v>
       </c>
       <c r="B18" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,32 +2690,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127784378</v>
+        <v>127781552</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>105516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2730,13 +2730,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654950</v>
+        <v>654841</v>
       </c>
       <c r="R19" t="n">
-        <v>6648519</v>
+        <v>6648625</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2805,7 +2805,7 @@
         <v>127781937</v>
       </c>
       <c r="B20" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>127782688</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>127781639</v>
       </c>
       <c r="B22" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>127782608</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>127782340</v>
       </c>
       <c r="B24" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>127783233</v>
       </c>
       <c r="B25" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>127781082</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>127783934</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>127784226</v>
       </c>
       <c r="B28" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>127781864</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>127780852</v>
       </c>
       <c r="B30" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>127782599</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>127784696</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>127781251</v>
       </c>
       <c r="B33" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4405,10 +4405,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127785581</v>
+        <v>127784246</v>
       </c>
       <c r="B34" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654763</v>
+        <v>654977</v>
       </c>
       <c r="R34" t="n">
-        <v>6648504</v>
+        <v>6648526</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4517,10 +4517,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127784246</v>
+        <v>127785581</v>
       </c>
       <c r="B35" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654977</v>
+        <v>654763</v>
       </c>
       <c r="R35" t="n">
-        <v>6648526</v>
+        <v>6648504</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4632,7 +4632,7 @@
         <v>127782582</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>127783185</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4853,10 +4853,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127782751</v>
+        <v>127784050</v>
       </c>
       <c r="B38" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4893,13 +4893,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654873</v>
+        <v>654933</v>
       </c>
       <c r="R38" t="n">
-        <v>6648648</v>
+        <v>6648492</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4938,12 +4938,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 25 bladrosetter.</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4970,10 +4965,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127784050</v>
+        <v>127782751</v>
       </c>
       <c r="B39" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5010,13 +5005,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654933</v>
+        <v>654873</v>
       </c>
       <c r="R39" t="n">
-        <v>6648492</v>
+        <v>6648648</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5045,7 +5040,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5055,7 +5050,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 25 bladrosetter.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5085,7 +5085,7 @@
         <v>127781723</v>
       </c>
       <c r="B40" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>127782237</v>
       </c>
       <c r="B41" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>127781429</v>
       </c>
       <c r="B42" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>127781898</v>
       </c>
       <c r="B43" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>127782716</v>
       </c>
       <c r="B44" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>127783424</v>
       </c>
       <c r="B45" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>127781122</v>
       </c>
       <c r="B46" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>127782650</v>
       </c>
       <c r="B47" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>127784278</v>
       </c>
       <c r="B48" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>127784001</v>
       </c>
       <c r="B49" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>127782845</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>127780501</v>
       </c>
       <c r="B51" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6461,60 +6461,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127785899</v>
+        <v>127781961</v>
       </c>
       <c r="B52" t="n">
-        <v>57832</v>
+        <v>98478</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654819</v>
+        <v>654782</v>
       </c>
       <c r="R52" t="n">
-        <v>6648643</v>
+        <v>6648543</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6543,7 +6536,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6553,12 +6546,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6585,10 +6573,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127781961</v>
+        <v>127782527</v>
       </c>
       <c r="B53" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6625,13 +6613,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654782</v>
+        <v>654840</v>
       </c>
       <c r="R53" t="n">
-        <v>6648543</v>
+        <v>6648555</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6660,7 +6648,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6670,7 +6658,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6697,53 +6685,60 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127782527</v>
+        <v>127785899</v>
       </c>
       <c r="B54" t="n">
-        <v>98470</v>
+        <v>57833</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654840</v>
+        <v>654819</v>
       </c>
       <c r="R54" t="n">
-        <v>6648555</v>
+        <v>6648643</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6772,7 +6767,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6782,7 +6777,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6812,7 +6812,7 @@
         <v>127782275</v>
       </c>
       <c r="B55" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6921,38 +6921,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127782436</v>
+        <v>127783912</v>
       </c>
       <c r="B56" t="n">
-        <v>98470</v>
+        <v>105516</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654829</v>
+        <v>654926</v>
       </c>
       <c r="R56" t="n">
-        <v>6648541</v>
+        <v>6648527</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7006,12 +7006,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:05</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7038,10 +7033,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127782081</v>
+        <v>127782436</v>
       </c>
       <c r="B57" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7078,13 +7073,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654807</v>
+        <v>654829</v>
       </c>
       <c r="R57" t="n">
-        <v>6648524</v>
+        <v>6648541</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7113,7 +7108,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7123,12 +7118,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>6 fröställn</t>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7155,38 +7150,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127783912</v>
+        <v>127782081</v>
       </c>
       <c r="B58" t="n">
-        <v>105508</v>
+        <v>98478</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7195,10 +7190,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654926</v>
+        <v>654807</v>
       </c>
       <c r="R58" t="n">
-        <v>6648527</v>
+        <v>6648524</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7230,7 +7225,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7240,7 +7235,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>6 fröställn</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -2461,10 +2461,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127784378</v>
+        <v>127781998</v>
       </c>
       <c r="B17" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654950</v>
+        <v>654769</v>
       </c>
       <c r="R17" t="n">
-        <v>6648519</v>
+        <v>6648529</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,7 +2546,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3 fröst.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,38 +2578,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127781998</v>
+        <v>127781552</v>
       </c>
       <c r="B18" t="n">
-        <v>98478</v>
+        <v>105609</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2613,13 +2618,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654769</v>
+        <v>654841</v>
       </c>
       <c r="R18" t="n">
-        <v>6648529</v>
+        <v>6648625</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2648,7 +2653,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,12 +2663,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>3 fröst.</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2690,32 +2690,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127781552</v>
+        <v>127784378</v>
       </c>
       <c r="B19" t="n">
-        <v>105516</v>
+        <v>98571</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2730,13 +2730,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654841</v>
+        <v>654950</v>
       </c>
       <c r="R19" t="n">
-        <v>6648625</v>
+        <v>6648519</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2802,10 +2802,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127781937</v>
+        <v>127782688</v>
       </c>
       <c r="B20" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654795</v>
+        <v>654896</v>
       </c>
       <c r="R20" t="n">
-        <v>6648542</v>
+        <v>6648627</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2887,7 +2887,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tiotalet bladrosetter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2914,10 +2919,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127782688</v>
+        <v>127781937</v>
       </c>
       <c r="B21" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2950,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2954,13 +2959,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654896</v>
+        <v>654795</v>
       </c>
       <c r="R21" t="n">
-        <v>6648627</v>
+        <v>6648542</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2989,7 +2994,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2999,12 +3004,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tiotalet bladrosetter.</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3034,7 +3034,7 @@
         <v>127781639</v>
       </c>
       <c r="B22" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782608</v>
+        <v>127782340</v>
       </c>
       <c r="B23" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654882</v>
+        <v>654840</v>
       </c>
       <c r="R23" t="n">
-        <v>6648586</v>
+        <v>6648541</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3228,7 +3228,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>5 fröst.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3255,10 +3260,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127782340</v>
+        <v>127782608</v>
       </c>
       <c r="B24" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3295,10 +3300,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654840</v>
+        <v>654882</v>
       </c>
       <c r="R24" t="n">
-        <v>6648541</v>
+        <v>6648586</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3330,7 +3335,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3340,12 +3345,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>5 fröst.</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3375,7 +3375,7 @@
         <v>127783233</v>
       </c>
       <c r="B25" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3489,10 +3489,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127781082</v>
+        <v>127783934</v>
       </c>
       <c r="B26" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654826</v>
+        <v>654911</v>
       </c>
       <c r="R26" t="n">
-        <v>6648657</v>
+        <v>6648510</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3574,12 +3574,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3606,10 +3601,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127783934</v>
+        <v>127781082</v>
       </c>
       <c r="B27" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3646,10 +3641,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654911</v>
+        <v>654826</v>
       </c>
       <c r="R27" t="n">
-        <v>6648510</v>
+        <v>6648657</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
@@ -3681,7 +3676,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3691,7 +3686,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3721,7 +3721,7 @@
         <v>127784226</v>
       </c>
       <c r="B28" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>127781864</v>
       </c>
       <c r="B29" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>127780852</v>
       </c>
       <c r="B30" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127782599</v>
+        <v>127785581</v>
       </c>
       <c r="B31" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654852</v>
+        <v>654763</v>
       </c>
       <c r="R31" t="n">
-        <v>6648592</v>
+        <v>6648504</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4176,10 +4176,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127784696</v>
+        <v>127782599</v>
       </c>
       <c r="B32" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4216,13 +4216,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654903</v>
+        <v>654852</v>
       </c>
       <c r="R32" t="n">
-        <v>6648470</v>
+        <v>6648592</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4291,7 +4291,7 @@
         <v>127781251</v>
       </c>
       <c r="B33" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>127784246</v>
       </c>
       <c r="B34" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127785581</v>
+        <v>127784696</v>
       </c>
       <c r="B35" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654763</v>
+        <v>654903</v>
       </c>
       <c r="R35" t="n">
-        <v>6648504</v>
+        <v>6648470</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4629,10 +4629,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127782582</v>
+        <v>127783185</v>
       </c>
       <c r="B36" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,24 +4658,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654831</v>
+        <v>654900</v>
       </c>
       <c r="R36" t="n">
-        <v>6648582</v>
+        <v>6648568</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4704,7 +4699,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4714,7 +4709,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127783185</v>
+        <v>127782582</v>
       </c>
       <c r="B37" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4770,19 +4770,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654900</v>
+        <v>654831</v>
       </c>
       <c r="R37" t="n">
-        <v>6648568</v>
+        <v>6648582</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4811,7 +4816,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4821,12 +4826,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Tall, kant av hänsynsyta inkluderande kalk renlavbergknalle ä, ett tiotal tallar och brant med aspar.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4856,7 +4856,7 @@
         <v>127784050</v>
       </c>
       <c r="B38" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>127782751</v>
       </c>
       <c r="B39" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127781723</v>
+        <v>127782237</v>
       </c>
       <c r="B40" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654831</v>
+        <v>654811</v>
       </c>
       <c r="R40" t="n">
-        <v>6648568</v>
+        <v>6648510</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,10 +5199,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127782237</v>
+        <v>127781429</v>
       </c>
       <c r="B41" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5239,13 +5239,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654811</v>
+        <v>654841</v>
       </c>
       <c r="R41" t="n">
-        <v>6648510</v>
+        <v>6648625</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5316,10 +5316,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127781429</v>
+        <v>127781898</v>
       </c>
       <c r="B42" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5356,13 +5356,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654841</v>
+        <v>654812</v>
       </c>
       <c r="R42" t="n">
-        <v>6648625</v>
+        <v>6648545</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Två fröställningar. 20-talet bladrosetter inom 4 m radie.</t>
+          <t>7 fröställn inom 3 m radie.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127781898</v>
+        <v>127781723</v>
       </c>
       <c r="B43" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654812</v>
+        <v>654831</v>
       </c>
       <c r="R43" t="n">
-        <v>6648545</v>
+        <v>6648568</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>7 fröställn inom 3 m radie.</t>
+          <t>Fyra fröst varav en som fortfarande har blommor i toppen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5553,7 +5553,7 @@
         <v>127782716</v>
       </c>
       <c r="B44" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>127783424</v>
       </c>
       <c r="B45" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>127781122</v>
       </c>
       <c r="B46" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127782650</v>
+        <v>127784278</v>
       </c>
       <c r="B47" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654890</v>
+        <v>654961</v>
       </c>
       <c r="R47" t="n">
-        <v>6648616</v>
+        <v>6648515</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6013,10 +6013,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127784278</v>
+        <v>127784001</v>
       </c>
       <c r="B48" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6053,13 +6053,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654961</v>
+        <v>654913</v>
       </c>
       <c r="R48" t="n">
-        <v>6648515</v>
+        <v>6648493</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6125,10 +6125,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127784001</v>
+        <v>127782650</v>
       </c>
       <c r="B49" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6165,10 +6165,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654913</v>
+        <v>654890</v>
       </c>
       <c r="R49" t="n">
-        <v>6648493</v>
+        <v>6648616</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6240,7 +6240,7 @@
         <v>127782845</v>
       </c>
       <c r="B50" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>127780501</v>
       </c>
       <c r="B51" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6461,53 +6461,60 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127781961</v>
+        <v>127785899</v>
       </c>
       <c r="B52" t="n">
-        <v>98478</v>
+        <v>57845</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654782</v>
+        <v>654819</v>
       </c>
       <c r="R52" t="n">
-        <v>6648543</v>
+        <v>6648643</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6536,7 +6543,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6546,7 +6553,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6573,10 +6585,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127782527</v>
+        <v>127781961</v>
       </c>
       <c r="B53" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6613,13 +6625,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654840</v>
+        <v>654782</v>
       </c>
       <c r="R53" t="n">
-        <v>6648555</v>
+        <v>6648543</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6648,7 +6660,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6658,7 +6670,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6685,60 +6697,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127785899</v>
+        <v>127782527</v>
       </c>
       <c r="B54" t="n">
-        <v>57833</v>
+        <v>98571</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654819</v>
+        <v>654840</v>
       </c>
       <c r="R54" t="n">
-        <v>6648643</v>
+        <v>6648555</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6767,7 +6772,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6777,12 +6782,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6812,7 +6812,7 @@
         <v>127782275</v>
       </c>
       <c r="B55" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6921,38 +6921,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127783912</v>
+        <v>127782081</v>
       </c>
       <c r="B56" t="n">
-        <v>105516</v>
+        <v>98571</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654926</v>
+        <v>654807</v>
       </c>
       <c r="R56" t="n">
-        <v>6648527</v>
+        <v>6648524</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7006,7 +7006,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>6 fröställn</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7036,7 +7041,7 @@
         <v>127782436</v>
       </c>
       <c r="B57" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7150,38 +7155,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127782081</v>
+        <v>127783912</v>
       </c>
       <c r="B58" t="n">
-        <v>98478</v>
+        <v>105609</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7190,10 +7195,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654807</v>
+        <v>654926</v>
       </c>
       <c r="R58" t="n">
-        <v>6648524</v>
+        <v>6648527</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7225,7 +7230,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7235,12 +7240,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>6 fröställn</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -2578,32 +2578,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127781552</v>
+        <v>127784378</v>
       </c>
       <c r="B18" t="n">
-        <v>105609</v>
+        <v>98571</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2618,13 +2618,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654841</v>
+        <v>654950</v>
       </c>
       <c r="R18" t="n">
-        <v>6648625</v>
+        <v>6648519</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2690,32 +2690,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127784378</v>
+        <v>127781552</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>105609</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2730,13 +2730,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654950</v>
+        <v>654841</v>
       </c>
       <c r="R19" t="n">
-        <v>6648519</v>
+        <v>6648625</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3372,38 +3372,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127783233</v>
+        <v>127783934</v>
       </c>
       <c r="B25" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654939</v>
+        <v>654911</v>
       </c>
       <c r="R25" t="n">
-        <v>6648547</v>
+        <v>6648510</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,12 +3457,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:52</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>I asp. Även bohål st hack.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3489,7 +3484,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127783934</v>
+        <v>127781082</v>
       </c>
       <c r="B26" t="n">
         <v>98571</v>
@@ -3529,10 +3524,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654911</v>
+        <v>654826</v>
       </c>
       <c r="R26" t="n">
-        <v>6648510</v>
+        <v>6648657</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3564,7 +3559,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3574,7 +3569,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3601,38 +3601,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127781082</v>
+        <v>127783233</v>
       </c>
       <c r="B27" t="n">
-        <v>98571</v>
+        <v>57682</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654826</v>
+        <v>654939</v>
       </c>
       <c r="R27" t="n">
-        <v>6648657</v>
+        <v>6648547</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Fyra kraftiga bladrosetter, ingen fröställning. Ca 5 m utanför, norr om snitslad hänsynsyta fuktstråk m socklar.</t>
+          <t>I asp. Även bohål st hack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -6461,60 +6461,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127785899</v>
+        <v>127781961</v>
       </c>
       <c r="B52" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654819</v>
+        <v>654782</v>
       </c>
       <c r="R52" t="n">
-        <v>6648643</v>
+        <v>6648543</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6543,7 +6536,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6553,12 +6546,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6585,7 +6573,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127781961</v>
+        <v>127782527</v>
       </c>
       <c r="B53" t="n">
         <v>98571</v>
@@ -6625,13 +6613,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654782</v>
+        <v>654840</v>
       </c>
       <c r="R53" t="n">
-        <v>6648543</v>
+        <v>6648555</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6660,7 +6648,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6670,7 +6658,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6697,53 +6685,60 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127782527</v>
+        <v>127785899</v>
       </c>
       <c r="B54" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654840</v>
+        <v>654819</v>
       </c>
       <c r="R54" t="n">
-        <v>6648555</v>
+        <v>6648643</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6772,7 +6767,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6782,7 +6777,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Tää tää lätet, minst två, troligen även ngn ungfågel.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7265,6 +7265,103 @@
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129705712</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>654912</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6648513</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -7270,7 +7270,7 @@
         <v>129705712</v>
       </c>
       <c r="B59" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -7270,7 +7270,7 @@
         <v>129705712</v>
       </c>
       <c r="B59" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -7270,7 +7270,7 @@
         <v>129705712</v>
       </c>
       <c r="B59" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -7270,7 +7270,7 @@
         <v>129705712</v>
       </c>
       <c r="B59" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -7270,7 +7270,7 @@
         <v>129705712</v>
       </c>
       <c r="B59" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -7270,7 +7270,7 @@
         <v>129705712</v>
       </c>
       <c r="B59" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -7270,7 +7270,7 @@
         <v>129705712</v>
       </c>
       <c r="B59" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -7270,7 +7270,7 @@
         <v>129705712</v>
       </c>
       <c r="B59" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -7270,7 +7270,7 @@
         <v>129705712</v>
       </c>
       <c r="B59" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -1548,7 +1548,7 @@
         <v>127126899</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127128041</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>127126721</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127127634</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127126633</v>
+        <v>127126872</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654796</v>
+        <v>654832</v>
       </c>
       <c r="R13" t="n">
-        <v>6648534</v>
+        <v>6648553</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127126872</v>
+        <v>127126633</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654832</v>
+        <v>654796</v>
       </c>
       <c r="R14" t="n">
-        <v>6648553</v>
+        <v>6648534</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>127127868</v>
       </c>
       <c r="B15" t="n">
-        <v>5177</v>
+        <v>5176</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>127126833</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>5196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -7478,10 +7478,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131735035</v>
+        <v>131735030</v>
       </c>
       <c r="B61" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654838</v>
+        <v>654824</v>
       </c>
       <c r="R61" t="n">
-        <v>6648618</v>
+        <v>6648579</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7588,10 +7588,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131735030</v>
+        <v>131735035</v>
       </c>
       <c r="B62" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654824</v>
+        <v>654838</v>
       </c>
       <c r="R62" t="n">
-        <v>6648579</v>
+        <v>6648618</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7701,7 +7701,7 @@
         <v>131735029</v>
       </c>
       <c r="B63" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>131735043</v>
       </c>
       <c r="B64" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>131735036</v>
       </c>
       <c r="B65" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>131735045</v>
       </c>
       <c r="B66" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>131735037</v>
       </c>
       <c r="B67" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>131735022</v>
       </c>
       <c r="B68" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>131735041</v>
       </c>
       <c r="B69" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>131735032</v>
       </c>
       <c r="B70" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>131735033</v>
       </c>
       <c r="B71" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>131735044</v>
       </c>
       <c r="B72" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>131735040</v>
       </c>
       <c r="B73" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>131735023</v>
       </c>
       <c r="B74" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>131735020</v>
       </c>
       <c r="B75" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9128,10 +9128,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131735026</v>
+        <v>131735031</v>
       </c>
       <c r="B76" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9167,10 +9167,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>654832</v>
+        <v>654825</v>
       </c>
       <c r="R76" t="n">
-        <v>6648579</v>
+        <v>6648587</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9238,10 +9238,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131735031</v>
+        <v>131735026</v>
       </c>
       <c r="B77" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9277,10 +9277,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>654825</v>
+        <v>654832</v>
       </c>
       <c r="R77" t="n">
-        <v>6648587</v>
+        <v>6648579</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9351,7 +9351,7 @@
         <v>131735034</v>
       </c>
       <c r="B78" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9458,10 +9458,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131735038</v>
+        <v>131735027</v>
       </c>
       <c r="B79" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9497,10 +9497,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>654882</v>
+        <v>654827</v>
       </c>
       <c r="R79" t="n">
-        <v>6648595</v>
+        <v>6648578</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9568,10 +9568,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131735027</v>
+        <v>131735018</v>
       </c>
       <c r="B80" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>654827</v>
+        <v>654785</v>
       </c>
       <c r="R80" t="n">
-        <v>6648578</v>
+        <v>6648514</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9678,10 +9678,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131735018</v>
+        <v>131735038</v>
       </c>
       <c r="B81" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9717,10 +9717,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>654785</v>
+        <v>654882</v>
       </c>
       <c r="R81" t="n">
-        <v>6648514</v>
+        <v>6648595</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9788,10 +9788,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131735024</v>
+        <v>131735046</v>
       </c>
       <c r="B82" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9827,10 +9827,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>654837</v>
+        <v>654869</v>
       </c>
       <c r="R82" t="n">
-        <v>6648572</v>
+        <v>6648636</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9898,10 +9898,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131735046</v>
+        <v>131735024</v>
       </c>
       <c r="B83" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>654869</v>
+        <v>654837</v>
       </c>
       <c r="R83" t="n">
-        <v>6648636</v>
+        <v>6648572</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9977,7 +9977,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10008,10 +10008,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131735049</v>
+        <v>131735025</v>
       </c>
       <c r="B84" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>654884</v>
+        <v>654838</v>
       </c>
       <c r="R84" t="n">
-        <v>6648649</v>
+        <v>6648577</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10118,10 +10118,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131735047</v>
+        <v>131735049</v>
       </c>
       <c r="B85" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10157,10 +10157,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>654878</v>
+        <v>654884</v>
       </c>
       <c r="R85" t="n">
-        <v>6648641</v>
+        <v>6648649</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10228,10 +10228,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131735025</v>
+        <v>131735047</v>
       </c>
       <c r="B86" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10267,10 +10267,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>654838</v>
+        <v>654878</v>
       </c>
       <c r="R86" t="n">
-        <v>6648577</v>
+        <v>6648641</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10341,7 +10341,7 @@
         <v>131735021</v>
       </c>
       <c r="B87" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>131735028</v>
       </c>
       <c r="B88" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>131735039</v>
       </c>
       <c r="B89" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>131735019</v>
       </c>
       <c r="B90" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>132124564</v>
       </c>
       <c r="B91" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>132124565</v>
       </c>
       <c r="B92" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -9458,7 +9458,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131735027</v>
+        <v>131735018</v>
       </c>
       <c r="B79" t="n">
         <v>99098</v>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9497,10 +9497,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>654827</v>
+        <v>654785</v>
       </c>
       <c r="R79" t="n">
-        <v>6648578</v>
+        <v>6648514</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9568,7 +9568,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131735018</v>
+        <v>131735038</v>
       </c>
       <c r="B80" t="n">
         <v>99098</v>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>654785</v>
+        <v>654882</v>
       </c>
       <c r="R80" t="n">
-        <v>6648514</v>
+        <v>6648595</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9678,7 +9678,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131735038</v>
+        <v>131735027</v>
       </c>
       <c r="B81" t="n">
         <v>99098</v>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9717,10 +9717,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>654882</v>
+        <v>654827</v>
       </c>
       <c r="R81" t="n">
-        <v>6648595</v>
+        <v>6648578</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -9458,7 +9458,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131735018</v>
+        <v>131735027</v>
       </c>
       <c r="B79" t="n">
         <v>99098</v>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9497,10 +9497,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>654785</v>
+        <v>654827</v>
       </c>
       <c r="R79" t="n">
-        <v>6648514</v>
+        <v>6648578</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9568,7 +9568,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131735038</v>
+        <v>131735018</v>
       </c>
       <c r="B80" t="n">
         <v>99098</v>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>654882</v>
+        <v>654785</v>
       </c>
       <c r="R80" t="n">
-        <v>6648595</v>
+        <v>6648514</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9678,7 +9678,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131735027</v>
+        <v>131735038</v>
       </c>
       <c r="B81" t="n">
         <v>99098</v>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9717,10 +9717,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>654827</v>
+        <v>654882</v>
       </c>
       <c r="R81" t="n">
-        <v>6648578</v>
+        <v>6648595</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -10781,7 +10781,7 @@
         <v>132124564</v>
       </c>
       <c r="B91" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>132124565</v>
       </c>
       <c r="B92" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -10781,7 +10781,7 @@
         <v>132124564</v>
       </c>
       <c r="B91" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>132124565</v>
       </c>
       <c r="B92" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -10781,7 +10781,7 @@
         <v>132124564</v>
       </c>
       <c r="B91" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>132124565</v>
       </c>
       <c r="B92" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -10781,7 +10781,7 @@
         <v>132124564</v>
       </c>
       <c r="B91" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>132124565</v>
       </c>
       <c r="B92" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -10781,7 +10781,7 @@
         <v>132124564</v>
       </c>
       <c r="B91" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>132124565</v>
       </c>
       <c r="B92" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 25604-2025 artfynd.xlsx
+++ b/artfynd/A 25604-2025 artfynd.xlsx
@@ -10781,7 +10781,7 @@
         <v>132124564</v>
       </c>
       <c r="B91" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>132124565</v>
       </c>
       <c r="B92" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
